--- a/data/proteomics/volume_size_ratio_across_compartment_NCB.xlsx
+++ b/data/proteomics/volume_size_ratio_across_compartment_NCB.xlsx
@@ -555,67 +555,67 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3535759548196252</v>
+        <v>0.3535759548196253</v>
       </c>
       <c r="D2" t="n">
-        <v>0.44993800635457</v>
+        <v>0.4499380063545704</v>
       </c>
       <c r="E2" t="n">
         <v>0.3960726307497776</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3764260891133207</v>
+        <v>0.3764260891133208</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3610210520158733</v>
+        <v>0.3610210520158732</v>
       </c>
       <c r="H2" t="n">
-        <v>0.3837629407785452</v>
+        <v>0.3837629407785449</v>
       </c>
       <c r="I2" t="n">
-        <v>0.3501971238950213</v>
+        <v>0.3501971238950212</v>
       </c>
       <c r="J2" t="n">
-        <v>0.345249188038294</v>
+        <v>0.3452491880382944</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3443600488278122</v>
+        <v>0.3443600488278124</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4241612809132655</v>
+        <v>0.4241612809132658</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3967779261609144</v>
+        <v>0.3967779261609142</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3646842743554957</v>
+        <v>0.3646842743554961</v>
       </c>
       <c r="O2" t="n">
-        <v>0.3621974669859341</v>
+        <v>0.3621974669859349</v>
       </c>
       <c r="P2" t="n">
-        <v>0.3386957220496927</v>
+        <v>0.3386957220496925</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3500044036367242</v>
+        <v>0.3500044036367241</v>
       </c>
       <c r="R2" t="n">
         <v>0.3581565371620418</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3881841720613279</v>
+        <v>0.3881841720613275</v>
       </c>
       <c r="T2" t="n">
-        <v>0.377050160005576</v>
+        <v>0.3770501600055758</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3749332900411703</v>
+        <v>0.37493329004117</v>
       </c>
       <c r="V2" t="n">
         <v>0.3716254486450846</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3935704211505097</v>
+        <v>0.3935704211505096</v>
       </c>
       <c r="X2" t="n">
         <v>0.3789353701496012</v>
@@ -649,7 +649,7 @@
         <v>0.002414048472221346</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00219581319853661</v>
+        <v>0.002195813198536611</v>
       </c>
       <c r="J3" t="n">
         <v>0.002054593952343794</v>
@@ -658,10 +658,10 @@
         <v>0.002046682197166993</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002315874979096807</v>
+        <v>0.002315874979096808</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002090797194957321</v>
+        <v>0.002090797194957322</v>
       </c>
       <c r="N3" t="n">
         <v>0.002048801028434855</v>
@@ -688,7 +688,7 @@
         <v>0.00121622562404132</v>
       </c>
       <c r="V3" t="n">
-        <v>0.001209425616235383</v>
+        <v>0.001209425616235382</v>
       </c>
       <c r="W3" t="n">
         <v>0.001212024624295441</v>
@@ -707,13 +707,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.002370032368170758</v>
+        <v>0.002370032368170757</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001041354470868797</v>
+        <v>0.001041354470868796</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001427645743623174</v>
+        <v>0.001427645743623175</v>
       </c>
       <c r="F4" t="n">
         <v>0.001486312862483832</v>
@@ -752,10 +752,10 @@
         <v>0.001513044241943896</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001536777005637497</v>
+        <v>0.001536777005637498</v>
       </c>
       <c r="S4" t="n">
-        <v>0.001530300882554727</v>
+        <v>0.001530300882554728</v>
       </c>
       <c r="T4" t="n">
         <v>0.001662291564781239</v>
@@ -859,43 +859,43 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.2234541096628679</v>
+        <v>0.2234541096628682</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2299940216053567</v>
+        <v>0.2299940216053569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2299711165877823</v>
+        <v>0.2299711165877824</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2203745407229897</v>
+        <v>0.2203745407229898</v>
       </c>
       <c r="G6" t="n">
         <v>0.2169298984097601</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2561538977238532</v>
+        <v>0.2561538977238531</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2240592664170036</v>
+        <v>0.2240592664170037</v>
       </c>
       <c r="J6" t="n">
         <v>0.2228546853306438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.2234823089109408</v>
+        <v>0.2234823089109407</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2217070220242957</v>
+        <v>0.2217070220242956</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2115299049006811</v>
+        <v>0.2115299049006814</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2073718472986694</v>
+        <v>0.2073718472986692</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2072352330153954</v>
+        <v>0.2072352330153953</v>
       </c>
       <c r="P6" t="n">
         <v>0.2238641239805663</v>
@@ -904,10 +904,10 @@
         <v>0.2229134844408277</v>
       </c>
       <c r="R6" t="n">
-        <v>0.220598427183937</v>
+        <v>0.2205984271839368</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2149790762630995</v>
+        <v>0.2149790762630992</v>
       </c>
       <c r="T6" t="n">
         <v>0.2138398886082433</v>
@@ -919,7 +919,7 @@
         <v>0.2129769074569823</v>
       </c>
       <c r="W6" t="n">
-        <v>0.2105647822704525</v>
+        <v>0.2105647822704524</v>
       </c>
       <c r="X6" t="n">
         <v>0.2147726243478232</v>
@@ -935,64 +935,64 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5849236469217903</v>
+        <v>0.5849236469217899</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5722356952149141</v>
+        <v>0.5722356952149145</v>
       </c>
       <c r="E7" t="n">
-        <v>0.595038622293928</v>
+        <v>0.5950386222939283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.608099441790566</v>
+        <v>0.6080994417905657</v>
       </c>
       <c r="G7" t="n">
-        <v>0.6166612449689953</v>
+        <v>0.6166612449689952</v>
       </c>
       <c r="H7" t="n">
-        <v>0.581830957820232</v>
+        <v>0.5818309578202323</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6011502110003687</v>
+        <v>0.6011502110003684</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6018763495131128</v>
+        <v>0.6018763495131126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6073699483167088</v>
+        <v>0.6073699483167103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5595216219357301</v>
+        <v>0.5595216219357296</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5680912689530682</v>
+        <v>0.5680912689530673</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5790083888229637</v>
+        <v>0.5790083888229633</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5895540126881001</v>
+        <v>0.5895540126881003</v>
       </c>
       <c r="P7" t="n">
-        <v>0.5931031783720256</v>
+        <v>0.5931031783720253</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.6082903655063039</v>
+        <v>0.6082903655063038</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6027489909596322</v>
+        <v>0.6027489909596317</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5884081128777993</v>
+        <v>0.5884081128777994</v>
       </c>
       <c r="T7" t="n">
-        <v>0.583599327363317</v>
+        <v>0.5835993273633174</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5895880991995033</v>
+        <v>0.5895880991995035</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5838315234267756</v>
+        <v>0.5838315234267749</v>
       </c>
       <c r="W7" t="n">
         <v>0.5640056513905358</v>
@@ -1011,46 +1011,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.2980964351906916</v>
+        <v>0.2980964351906911</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3926402697565813</v>
+        <v>0.3926402697565811</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3347955550153732</v>
+        <v>0.3347955550153734</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3372460225356294</v>
+        <v>0.3372460225356292</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3270834516589479</v>
+        <v>0.3270834516589478</v>
       </c>
       <c r="H8" t="n">
         <v>0.32455741372762</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3147561731118687</v>
+        <v>0.3147561731118685</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3117458622841415</v>
+        <v>0.3117458622841416</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3087309703726737</v>
+        <v>0.3087309703726736</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3070463006244882</v>
+        <v>0.3070463006244887</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2964983367100264</v>
+        <v>0.2964983367100265</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2785363316639129</v>
+        <v>0.2785363316639128</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2889796908036825</v>
+        <v>0.2889796908036829</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2804748910854183</v>
+        <v>0.2804748910854186</v>
       </c>
       <c r="Q8" t="n">
         <v>0.2909664381417778</v>
@@ -1059,19 +1059,19 @@
         <v>0.3003948641606259</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3233472239867044</v>
+        <v>0.3233472239867042</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3268754391666824</v>
+        <v>0.3268754391666825</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3267202021077714</v>
+        <v>0.3267202021077716</v>
       </c>
       <c r="V8" t="n">
-        <v>0.3230180978221791</v>
+        <v>0.3230180978221788</v>
       </c>
       <c r="W8" t="n">
-        <v>0.3293162441981488</v>
+        <v>0.3293162441981489</v>
       </c>
       <c r="X8" t="n">
         <v>0.3128979531053259</v>
@@ -1093,7 +1093,7 @@
         <v>0.02563390296351621</v>
       </c>
       <c r="E9" t="n">
-        <v>0.02684130695231574</v>
+        <v>0.02684130695231573</v>
       </c>
       <c r="F9" t="n">
         <v>0.02578781491721168</v>
@@ -1126,7 +1126,7 @@
         <v>0.02521062330496876</v>
       </c>
       <c r="P9" t="n">
-        <v>0.03378805264547833</v>
+        <v>0.03378805264547834</v>
       </c>
       <c r="Q9" t="n">
         <v>0.02547268139973191</v>
@@ -1141,7 +1141,7 @@
         <v>0.02412682654836499</v>
       </c>
       <c r="U9" t="n">
-        <v>0.02377202857525005</v>
+        <v>0.02377202857525004</v>
       </c>
       <c r="V9" t="n">
         <v>0.0245779916154002</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.04969601081663156</v>
+        <v>0.04969601081663158</v>
       </c>
       <c r="D11" t="n">
         <v>0.1200357388053042</v>
@@ -1254,19 +1254,19 @@
         <v>0.04032572677457306</v>
       </c>
       <c r="H11" t="n">
-        <v>0.05724340867815018</v>
+        <v>0.05724340867815017</v>
       </c>
       <c r="I11" t="n">
         <v>0.03303273997864271</v>
       </c>
       <c r="J11" t="n">
-        <v>0.03416589408807952</v>
+        <v>0.03416589408807951</v>
       </c>
       <c r="K11" t="n">
-        <v>0.03506990992970054</v>
+        <v>0.03506990992970055</v>
       </c>
       <c r="L11" t="n">
-        <v>0.059113181701626</v>
+        <v>0.05911318170162601</v>
       </c>
       <c r="M11" t="n">
         <v>0.04734241399618419</v>
@@ -1275,10 +1275,10 @@
         <v>0.03698292688339516</v>
       </c>
       <c r="O11" t="n">
-        <v>0.03469383510722185</v>
+        <v>0.03469383510722184</v>
       </c>
       <c r="P11" t="n">
-        <v>0.03980523856770422</v>
+        <v>0.03980523856770423</v>
       </c>
       <c r="Q11" t="n">
         <v>0.03188726306510711</v>
@@ -1290,13 +1290,13 @@
         <v>0.05900168473310421</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0611967677679628</v>
+        <v>0.06119676776796282</v>
       </c>
       <c r="U11" t="n">
-        <v>0.06319339197001848</v>
+        <v>0.06319339197001847</v>
       </c>
       <c r="V11" t="n">
-        <v>0.06182197545208699</v>
+        <v>0.06182197545208698</v>
       </c>
       <c r="W11" t="n">
         <v>0.088396724010533</v>
@@ -1315,34 +1315,34 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03422250760324074</v>
+        <v>0.03422250760324073</v>
       </c>
       <c r="D12" t="n">
-        <v>0.02715912638044258</v>
+        <v>0.02715912638044257</v>
       </c>
       <c r="E12" t="n">
         <v>0.03059498696097303</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02926344473020535</v>
+        <v>0.02926344473020537</v>
       </c>
       <c r="G12" t="n">
         <v>0.02684793593971771</v>
       </c>
       <c r="H12" t="n">
-        <v>0.03407751181992189</v>
+        <v>0.03407751181992187</v>
       </c>
       <c r="I12" t="n">
-        <v>0.03219753116497482</v>
+        <v>0.0321975311649748</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0345990437323757</v>
+        <v>0.03459904373237572</v>
       </c>
       <c r="K12" t="n">
-        <v>0.03191853776239084</v>
+        <v>0.03191853776239083</v>
       </c>
       <c r="L12" t="n">
-        <v>0.03261084328857178</v>
+        <v>0.03261084328857179</v>
       </c>
       <c r="M12" t="n">
         <v>0.03414680014285833</v>
@@ -1357,19 +1357,19 @@
         <v>0.03222177576272105</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02913391414455592</v>
+        <v>0.02913391414455593</v>
       </c>
       <c r="R12" t="n">
-        <v>0.02889390425015979</v>
+        <v>0.02889390425015977</v>
       </c>
       <c r="S12" t="n">
-        <v>0.03038567992344558</v>
+        <v>0.03038567992344557</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03574401689663668</v>
+        <v>0.03574401689663666</v>
       </c>
       <c r="U12" t="n">
-        <v>0.03289669089527896</v>
+        <v>0.03289669089527897</v>
       </c>
       <c r="V12" t="n">
         <v>0.03610690849407314</v>
@@ -1378,7 +1378,7 @@
         <v>0.02798919809832174</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03120334772689894</v>
+        <v>0.03120334772689895</v>
       </c>
     </row>
     <row r="13">
@@ -1394,16 +1394,16 @@
         <v>0.003066687474607211</v>
       </c>
       <c r="D13" t="n">
-        <v>0.001927480690258628</v>
+        <v>0.001927480690258629</v>
       </c>
       <c r="E13" t="n">
-        <v>0.002329473405025954</v>
+        <v>0.002329473405025955</v>
       </c>
       <c r="F13" t="n">
         <v>0.002448658017407294</v>
       </c>
       <c r="G13" t="n">
-        <v>0.002099551478423174</v>
+        <v>0.002099551478423173</v>
       </c>
       <c r="H13" t="n">
         <v>0.004636272534310303</v>
@@ -1415,13 +1415,13 @@
         <v>0.00522837497120539</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00382402866825016</v>
+        <v>0.003824028668250161</v>
       </c>
       <c r="L13" t="n">
-        <v>0.002715856037654478</v>
+        <v>0.002715856037654477</v>
       </c>
       <c r="M13" t="n">
-        <v>0.003216338637950884</v>
+        <v>0.003216338637950885</v>
       </c>
       <c r="N13" t="n">
         <v>0.00337118984369213</v>
@@ -1442,7 +1442,7 @@
         <v>0.00195509788920702</v>
       </c>
       <c r="T13" t="n">
-        <v>0.002062984595257346</v>
+        <v>0.002062984595257347</v>
       </c>
       <c r="U13" t="n">
         <v>0.001837895897234728</v>
@@ -1451,10 +1451,10 @@
         <v>0.001861851137432451</v>
       </c>
       <c r="W13" t="n">
-        <v>0.001788628493051511</v>
+        <v>0.001788628493051512</v>
       </c>
       <c r="X13" t="n">
-        <v>0.002036971942003091</v>
+        <v>0.00203697194200309</v>
       </c>
     </row>
     <row r="14">
@@ -1473,7 +1473,7 @@
         <v>0.01535421547884846</v>
       </c>
       <c r="E14" t="n">
-        <v>0.01648277373402393</v>
+        <v>0.01648277373402392</v>
       </c>
       <c r="F14" t="n">
         <v>0.01408324403061064</v>
@@ -1482,10 +1482,10 @@
         <v>0.01323155678816376</v>
       </c>
       <c r="H14" t="n">
-        <v>0.02027826192387627</v>
+        <v>0.02027826192387626</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01695904612001691</v>
+        <v>0.01695904612001692</v>
       </c>
       <c r="J14" t="n">
         <v>0.01574969253881931</v>
@@ -1494,13 +1494,13 @@
         <v>0.01434977407364279</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02112385438072973</v>
+        <v>0.02112385438072974</v>
       </c>
       <c r="M14" t="n">
         <v>0.02047084709852667</v>
       </c>
       <c r="N14" t="n">
-        <v>0.0186862020271372</v>
+        <v>0.01868620202713721</v>
       </c>
       <c r="O14" t="n">
         <v>0.01814686146397517</v>
@@ -1512,7 +1512,7 @@
         <v>0.01518199650236766</v>
       </c>
       <c r="R14" t="n">
-        <v>0.01542367061525993</v>
+        <v>0.01542367061525992</v>
       </c>
       <c r="S14" t="n">
         <v>0.01597095803290573</v>
@@ -1530,7 +1530,7 @@
         <v>0.01514633542090706</v>
       </c>
       <c r="X14" t="n">
-        <v>0.01568301161136809</v>
+        <v>0.0156830116113681</v>
       </c>
     </row>
     <row r="15">
@@ -1549,10 +1549,10 @@
         <v>0.005737078838824729</v>
       </c>
       <c r="E15" t="n">
-        <v>0.006053325197211692</v>
+        <v>0.006053325197211693</v>
       </c>
       <c r="F15" t="n">
-        <v>0.00490961634556713</v>
+        <v>0.004909616345567129</v>
       </c>
       <c r="G15" t="n">
         <v>0.004321735647221314</v>
@@ -1591,7 +1591,7 @@
         <v>0.004953625971004525</v>
       </c>
       <c r="S15" t="n">
-        <v>0.005575064665052231</v>
+        <v>0.005575064665052232</v>
       </c>
       <c r="T15" t="n">
         <v>0.004523862315083484</v>
@@ -1600,13 +1600,13 @@
         <v>0.004427377662100111</v>
       </c>
       <c r="V15" t="n">
-        <v>0.00430681364434418</v>
+        <v>0.004306813644344179</v>
       </c>
       <c r="W15" t="n">
         <v>0.005300678722696237</v>
       </c>
       <c r="X15" t="n">
-        <v>0.005235835398570705</v>
+        <v>0.005235835398570704</v>
       </c>
     </row>
     <row r="16">
@@ -1628,10 +1628,10 @@
         <v>0.01117299082266391</v>
       </c>
       <c r="F16" t="n">
-        <v>0.008753593475846432</v>
+        <v>0.008753593475846429</v>
       </c>
       <c r="G16" t="n">
-        <v>0.007069984352760147</v>
+        <v>0.007069984352760149</v>
       </c>
       <c r="H16" t="n">
         <v>0.006993925471469262</v>
@@ -1655,19 +1655,19 @@
         <v>0.007099898624590015</v>
       </c>
       <c r="O16" t="n">
-        <v>0.00720758699263342</v>
+        <v>0.007207586992633419</v>
       </c>
       <c r="P16" t="n">
-        <v>0.008731129632282153</v>
+        <v>0.008731129632282151</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.009213859178254595</v>
+        <v>0.009213859178254593</v>
       </c>
       <c r="R16" t="n">
-        <v>0.009095329846948792</v>
+        <v>0.00909532984694879</v>
       </c>
       <c r="S16" t="n">
-        <v>0.008742754760217828</v>
+        <v>0.008742754760217826</v>
       </c>
       <c r="T16" t="n">
         <v>0.009933160257855648</v>
@@ -1679,7 +1679,7 @@
         <v>0.01006415948046557</v>
       </c>
       <c r="W16" t="n">
-        <v>0.009575832726463769</v>
+        <v>0.009575832726463767</v>
       </c>
       <c r="X16" t="n">
         <v>0.009382492030232623</v>
@@ -1695,13 +1695,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.003773274890232518</v>
+        <v>0.003773274890232519</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002551500577883038</v>
+        <v>0.002551500577883037</v>
       </c>
       <c r="E17" t="n">
-        <v>0.003148599071098714</v>
+        <v>0.003148599071098715</v>
       </c>
       <c r="F17" t="n">
         <v>0.002579140841804989</v>
@@ -1713,28 +1713,28 @@
         <v>0.003948734053349769</v>
       </c>
       <c r="I17" t="n">
-        <v>0.003185130918206695</v>
+        <v>0.003185130918206696</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00332714021815563</v>
+        <v>0.003327140218155629</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00320687093478918</v>
+        <v>0.003206870934789179</v>
       </c>
       <c r="L17" t="n">
-        <v>0.004606146363200561</v>
+        <v>0.00460614636320056</v>
       </c>
       <c r="M17" t="n">
-        <v>0.004184681860339337</v>
+        <v>0.004184681860339338</v>
       </c>
       <c r="N17" t="n">
-        <v>0.003251242707448071</v>
+        <v>0.003251242707448069</v>
       </c>
       <c r="O17" t="n">
         <v>0.003295730813923053</v>
       </c>
       <c r="P17" t="n">
-        <v>0.002801890152787184</v>
+        <v>0.002801890152787187</v>
       </c>
       <c r="Q17" t="n">
         <v>0.002435899617473696</v>
@@ -1774,55 +1774,55 @@
         <v>0.006639899205647713</v>
       </c>
       <c r="D18" t="n">
-        <v>0.005110031664121886</v>
+        <v>0.005110031664121885</v>
       </c>
       <c r="E18" t="n">
         <v>0.005871074122555968</v>
       </c>
       <c r="F18" t="n">
-        <v>0.005596023862015608</v>
+        <v>0.005596023862015606</v>
       </c>
       <c r="G18" t="n">
-        <v>0.005076998952434327</v>
+        <v>0.005076998952434325</v>
       </c>
       <c r="H18" t="n">
-        <v>0.006464167582216737</v>
+        <v>0.006464167582216739</v>
       </c>
       <c r="I18" t="n">
         <v>0.005849171278071589</v>
       </c>
       <c r="J18" t="n">
-        <v>0.006410023461929362</v>
+        <v>0.006410023461929364</v>
       </c>
       <c r="K18" t="n">
-        <v>0.006296844024290613</v>
+        <v>0.006296844024290614</v>
       </c>
       <c r="L18" t="n">
-        <v>0.00659775258848727</v>
+        <v>0.006597752588487271</v>
       </c>
       <c r="M18" t="n">
-        <v>0.006847734605606452</v>
+        <v>0.006847734605606454</v>
       </c>
       <c r="N18" t="n">
-        <v>0.00693762670480742</v>
+        <v>0.006937626704807421</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006447254927164285</v>
+        <v>0.006447254927164286</v>
       </c>
       <c r="P18" t="n">
         <v>0.005419866844523195</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.004312831069589305</v>
+        <v>0.004312831069589306</v>
       </c>
       <c r="R18" t="n">
-        <v>0.004143846253288053</v>
+        <v>0.004143846253288051</v>
       </c>
       <c r="S18" t="n">
         <v>0.004138882041359804</v>
       </c>
       <c r="T18" t="n">
-        <v>0.004350896388617447</v>
+        <v>0.004350896388617446</v>
       </c>
       <c r="U18" t="n">
         <v>0.00388854464747261</v>
@@ -1831,7 +1831,7 @@
         <v>0.004420695811336244</v>
       </c>
       <c r="W18" t="n">
-        <v>0.004026785210178555</v>
+        <v>0.004026785210178554</v>
       </c>
       <c r="X18" t="n">
         <v>0.004444062079457313</v>
@@ -1847,70 +1847,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.009721406686271514</v>
+        <v>0.009721406686271515</v>
       </c>
       <c r="D19" t="n">
-        <v>0.006510587801925468</v>
+        <v>0.006510587801925466</v>
       </c>
       <c r="E19" t="n">
         <v>0.007410392463733688</v>
       </c>
       <c r="F19" t="n">
-        <v>0.007004217147386076</v>
+        <v>0.007004217147386074</v>
       </c>
       <c r="G19" t="n">
-        <v>0.006429180696344208</v>
+        <v>0.006429180696344207</v>
       </c>
       <c r="H19" t="n">
-        <v>0.00853116388367872</v>
+        <v>0.008531163883678718</v>
       </c>
       <c r="I19" t="n">
-        <v>0.007684530107722517</v>
+        <v>0.00768453010772252</v>
       </c>
       <c r="J19" t="n">
-        <v>0.008290712640100173</v>
+        <v>0.008290712640100175</v>
       </c>
       <c r="K19" t="n">
-        <v>0.008080676176606197</v>
+        <v>0.008080676176606199</v>
       </c>
       <c r="L19" t="n">
         <v>0.008538601492283299</v>
       </c>
       <c r="M19" t="n">
-        <v>0.008542301487374095</v>
+        <v>0.008542301487374096</v>
       </c>
       <c r="N19" t="n">
-        <v>0.008575710547622826</v>
+        <v>0.008575710547622828</v>
       </c>
       <c r="O19" t="n">
         <v>0.007874514944403463</v>
       </c>
       <c r="P19" t="n">
-        <v>0.007756030462897569</v>
+        <v>0.007756030462897566</v>
       </c>
       <c r="Q19" t="n">
         <v>0.005257393969553537</v>
       </c>
       <c r="R19" t="n">
-        <v>0.004986637632994619</v>
+        <v>0.004986637632994618</v>
       </c>
       <c r="S19" t="n">
         <v>0.005193559975196623</v>
       </c>
       <c r="T19" t="n">
-        <v>0.005553118265819453</v>
+        <v>0.005553118265819455</v>
       </c>
       <c r="U19" t="n">
-        <v>0.004771015978944614</v>
+        <v>0.004771015978944615</v>
       </c>
       <c r="V19" t="n">
         <v>0.005614222817095837</v>
       </c>
       <c r="W19" t="n">
-        <v>0.004974691791471387</v>
+        <v>0.004974691791471388</v>
       </c>
       <c r="X19" t="n">
-        <v>0.005728284960979942</v>
+        <v>0.005728284960979943</v>
       </c>
     </row>
     <row r="20">
@@ -1923,7 +1923,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.01560059346369617</v>
+        <v>0.01560059346369616</v>
       </c>
       <c r="D20" t="n">
         <v>0.01190049221100687</v>
@@ -1938,7 +1938,7 @@
         <v>0.01505011426928739</v>
       </c>
       <c r="H20" t="n">
-        <v>0.01524404270481393</v>
+        <v>0.01524404270481392</v>
       </c>
       <c r="I20" t="n">
         <v>0.01591646533259021</v>
@@ -2078,7 +2078,7 @@
         <v>0.002557891581254954</v>
       </c>
       <c r="D22" t="n">
-        <v>0.00146451573386159</v>
+        <v>0.001464515733861591</v>
       </c>
       <c r="E22" t="n">
         <v>0.001872073132974885</v>
@@ -2090,7 +2090,7 @@
         <v>0.001405090340726034</v>
       </c>
       <c r="H22" t="n">
-        <v>0.002098451595485453</v>
+        <v>0.002098451595485452</v>
       </c>
       <c r="I22" t="n">
         <v>0.001839746123586356</v>
@@ -2102,7 +2102,7 @@
         <v>0.001788760347721757</v>
       </c>
       <c r="L22" t="n">
-        <v>0.00228290734556501</v>
+        <v>0.002282907345565011</v>
       </c>
       <c r="M22" t="n">
         <v>0.001963869534333443</v>
@@ -2114,10 +2114,10 @@
         <v>0.001615652620310242</v>
       </c>
       <c r="P22" t="n">
-        <v>0.002082951265287436</v>
+        <v>0.002082951265287435</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.001826010654251464</v>
+        <v>0.001826010654251465</v>
       </c>
       <c r="R22" t="n">
         <v>0.001801458769248037</v>
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.0413249214707265</v>
+        <v>0.04132492147072653</v>
       </c>
       <c r="D23" t="n">
         <v>0.1072628382194369</v>
@@ -2160,13 +2160,13 @@
         <v>0.05057577607063637</v>
       </c>
       <c r="F23" t="n">
-        <v>0.04362490591889873</v>
+        <v>0.04362490591889874</v>
       </c>
       <c r="G23" t="n">
         <v>0.0323516008925834</v>
       </c>
       <c r="H23" t="n">
-        <v>0.04278553702893146</v>
+        <v>0.04278553702893145</v>
       </c>
       <c r="I23" t="n">
         <v>0.02755553702002873</v>
@@ -2187,7 +2187,7 @@
         <v>0.02857904452403258</v>
       </c>
       <c r="O23" t="n">
-        <v>0.02642018718078058</v>
+        <v>0.02642018718078059</v>
       </c>
       <c r="P23" t="n">
         <v>0.03195771667275057</v>
@@ -2196,25 +2196,25 @@
         <v>0.02459266707630608</v>
       </c>
       <c r="R23" t="n">
-        <v>0.03109871881203529</v>
+        <v>0.0310987188120353</v>
       </c>
       <c r="S23" t="n">
         <v>0.05096784782332236</v>
       </c>
       <c r="T23" t="n">
-        <v>0.05537067675459085</v>
+        <v>0.05537067675459086</v>
       </c>
       <c r="U23" t="n">
-        <v>0.0581972945414689</v>
+        <v>0.05819729454146891</v>
       </c>
       <c r="V23" t="n">
         <v>0.05616489424395726</v>
       </c>
       <c r="W23" t="n">
-        <v>0.08011382237063122</v>
+        <v>0.08011382237063119</v>
       </c>
       <c r="X23" t="n">
-        <v>0.03916493319153775</v>
+        <v>0.03916493319153776</v>
       </c>
     </row>
     <row r="24">
@@ -2266,7 +2266,7 @@
         <v>0.0004898241487102991</v>
       </c>
       <c r="P24" t="n">
-        <v>0.0002728026624539165</v>
+        <v>0.0002728026624539166</v>
       </c>
       <c r="Q24" t="n">
         <v>4.194339977471851e-05</v>
@@ -2306,16 +2306,16 @@
         <v>0.004313295770544396</v>
       </c>
       <c r="D25" t="n">
-        <v>0.003985874861486827</v>
+        <v>0.003985874861486826</v>
       </c>
       <c r="E25" t="n">
-        <v>0.004880653133137252</v>
+        <v>0.00488065313313725</v>
       </c>
       <c r="F25" t="n">
-        <v>0.003985311391305411</v>
+        <v>0.003985311391305412</v>
       </c>
       <c r="G25" t="n">
-        <v>0.003634475108667416</v>
+        <v>0.003634475108667415</v>
       </c>
       <c r="H25" t="n">
         <v>0.005472387278652143</v>
@@ -2339,10 +2339,10 @@
         <v>0.004467116713884198</v>
       </c>
       <c r="O25" t="n">
-        <v>0.004231998863336004</v>
+        <v>0.004231998863336005</v>
       </c>
       <c r="P25" t="n">
-        <v>0.00351880245941052</v>
+        <v>0.003518802459410519</v>
       </c>
       <c r="Q25" t="n">
         <v>0.00343101343104472</v>
@@ -2360,10 +2360,10 @@
         <v>0.003113128657735178</v>
       </c>
       <c r="V25" t="n">
-        <v>0.003351233673478891</v>
+        <v>0.00335123367347889</v>
       </c>
       <c r="W25" t="n">
-        <v>0.003174164399062236</v>
+        <v>0.003174164399062235</v>
       </c>
       <c r="X25" t="n">
         <v>0.003294323885245528</v>
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>0.003049600769415177</v>
+        <v>0.003049600769415178</v>
       </c>
       <c r="D26" t="n">
         <v>0.002289932753811677</v>
@@ -2391,13 +2391,13 @@
         <v>0.002565310878654197</v>
       </c>
       <c r="G26" t="n">
-        <v>0.002309606247375076</v>
+        <v>0.002309606247375075</v>
       </c>
       <c r="H26" t="n">
         <v>0.003028660095418494</v>
       </c>
       <c r="I26" t="n">
-        <v>0.002718840386510685</v>
+        <v>0.002718840386510686</v>
       </c>
       <c r="J26" t="n">
         <v>0.00297798254378455</v>
@@ -2412,13 +2412,13 @@
         <v>0.002811093570044107</v>
       </c>
       <c r="N26" t="n">
-        <v>0.002833646353202518</v>
+        <v>0.002833646353202517</v>
       </c>
       <c r="O26" t="n">
-        <v>0.00263410044322387</v>
+        <v>0.002634100443223871</v>
       </c>
       <c r="P26" t="n">
-        <v>0.002676057720771624</v>
+        <v>0.002676057720771623</v>
       </c>
       <c r="Q26" t="n">
         <v>0.001623798388497108</v>
@@ -2439,7 +2439,7 @@
         <v>0.001988497244057694</v>
       </c>
       <c r="W26" t="n">
-        <v>0.001597480591768938</v>
+        <v>0.001597480591768937</v>
       </c>
       <c r="X26" t="n">
         <v>0.002130370249908595</v>
@@ -2458,37 +2458,37 @@
         <v>0.02085696964794523</v>
       </c>
       <c r="D27" t="n">
-        <v>0.01401002145768241</v>
+        <v>0.0140100214576824</v>
       </c>
       <c r="E27" t="n">
-        <v>0.02014947006697496</v>
+        <v>0.02014947006697497</v>
       </c>
       <c r="F27" t="n">
-        <v>0.02035755968804774</v>
+        <v>0.02035755968804775</v>
       </c>
       <c r="G27" t="n">
-        <v>0.02155684375335817</v>
+        <v>0.02155684375335818</v>
       </c>
       <c r="H27" t="n">
         <v>0.01537225004465057</v>
       </c>
       <c r="I27" t="n">
-        <v>0.01876707044612369</v>
+        <v>0.01876707044612368</v>
       </c>
       <c r="J27" t="n">
-        <v>0.0191111018397034</v>
+        <v>0.01911110183970339</v>
       </c>
       <c r="K27" t="n">
         <v>0.02097961291055484</v>
       </c>
       <c r="L27" t="n">
-        <v>0.01843038288699763</v>
+        <v>0.01843038288699762</v>
       </c>
       <c r="M27" t="n">
-        <v>0.01955270895078725</v>
+        <v>0.01955270895078726</v>
       </c>
       <c r="N27" t="n">
-        <v>0.02183579810893636</v>
+        <v>0.02183579810893635</v>
       </c>
       <c r="O27" t="n">
         <v>0.02151457866934889</v>
@@ -2500,16 +2500,16 @@
         <v>0.0295864962710626</v>
       </c>
       <c r="R27" t="n">
-        <v>0.02782137365847301</v>
+        <v>0.027821373658473</v>
       </c>
       <c r="S27" t="n">
-        <v>0.02411109198346139</v>
+        <v>0.02411109198346141</v>
       </c>
       <c r="T27" t="n">
-        <v>0.02609653837668158</v>
+        <v>0.02609653837668157</v>
       </c>
       <c r="U27" t="n">
-        <v>0.02709497926330411</v>
+        <v>0.02709497926330412</v>
       </c>
       <c r="V27" t="n">
         <v>0.02765904725778252</v>
@@ -2518,7 +2518,7 @@
         <v>0.02574355374125664</v>
       </c>
       <c r="X27" t="n">
-        <v>0.02602412586808692</v>
+        <v>0.02602412586808691</v>
       </c>
     </row>
     <row r="28">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.00220248222518394</v>
+        <v>0.002202482225183942</v>
       </c>
       <c r="D28" t="n">
-        <v>0.001445413050843881</v>
+        <v>0.00144541305084388</v>
       </c>
       <c r="E28" t="n">
         <v>0.001782529507186899</v>
@@ -2555,7 +2555,7 @@
         <v>0.001903199229231592</v>
       </c>
       <c r="K28" t="n">
-        <v>0.001924123013641033</v>
+        <v>0.001924123013641034</v>
       </c>
       <c r="L28" t="n">
         <v>0.001669927753078548</v>
@@ -2564,7 +2564,7 @@
         <v>0.001730914916551749</v>
       </c>
       <c r="N28" t="n">
-        <v>0.001791531963698043</v>
+        <v>0.001791531963698044</v>
       </c>
       <c r="O28" t="n">
         <v>0.001657963631220712</v>
@@ -2607,13 +2607,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.0238902443830255</v>
+        <v>0.02389024438302548</v>
       </c>
       <c r="D29" t="n">
         <v>0.02067358793367684</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02286103106362509</v>
+        <v>0.02286103106362508</v>
       </c>
       <c r="F29" t="n">
         <v>0.0213551492320058</v>
@@ -2625,25 +2625,25 @@
         <v>0.03431051229429368</v>
       </c>
       <c r="I29" t="n">
-        <v>0.02228654120362334</v>
+        <v>0.02228654120362335</v>
       </c>
       <c r="J29" t="n">
-        <v>0.02297012997199001</v>
+        <v>0.02297012997199003</v>
       </c>
       <c r="K29" t="n">
         <v>0.02151357890968796</v>
       </c>
       <c r="L29" t="n">
-        <v>0.0245634423143973</v>
+        <v>0.02456344231439729</v>
       </c>
       <c r="M29" t="n">
         <v>0.02253810220741005</v>
       </c>
       <c r="N29" t="n">
-        <v>0.02315006268526183</v>
+        <v>0.02315006268526182</v>
       </c>
       <c r="O29" t="n">
-        <v>0.02211810869760355</v>
+        <v>0.02211810869760356</v>
       </c>
       <c r="P29" t="n">
         <v>0.02182576031811186</v>
@@ -2661,7 +2661,7 @@
         <v>0.01549332176667433</v>
       </c>
       <c r="U29" t="n">
-        <v>0.01447378763365433</v>
+        <v>0.01447378763365432</v>
       </c>
       <c r="V29" t="n">
         <v>0.01596580055455807</v>
@@ -2803,70 +2803,70 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.06323354183969876</v>
+        <v>0.06323354183969879</v>
       </c>
       <c r="D32" t="n">
-        <v>0.06363536262427674</v>
+        <v>0.06363536262427676</v>
       </c>
       <c r="E32" t="n">
-        <v>0.06527018244650516</v>
+        <v>0.06527018244650518</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06820168490753992</v>
+        <v>0.0682016849075399</v>
       </c>
       <c r="G32" t="n">
-        <v>0.06996186710052145</v>
+        <v>0.06996186710052144</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0610289302358032</v>
+        <v>0.06102893023580322</v>
       </c>
       <c r="I32" t="n">
         <v>0.06804003446008791</v>
       </c>
       <c r="J32" t="n">
-        <v>0.06839747905950877</v>
+        <v>0.06839747905950881</v>
       </c>
       <c r="K32" t="n">
-        <v>0.06872030206599877</v>
+        <v>0.0687203020659988</v>
       </c>
       <c r="L32" t="n">
-        <v>0.06271521739608726</v>
+        <v>0.06271521739608729</v>
       </c>
       <c r="M32" t="n">
-        <v>0.0668246223066499</v>
+        <v>0.06682462230664989</v>
       </c>
       <c r="N32" t="n">
-        <v>0.07492745835726884</v>
+        <v>0.07492745835726883</v>
       </c>
       <c r="O32" t="n">
-        <v>0.07367425406922909</v>
+        <v>0.0736742540692291</v>
       </c>
       <c r="P32" t="n">
-        <v>0.06833079927644542</v>
+        <v>0.06833079927644543</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.07880267442060017</v>
+        <v>0.07880267442060016</v>
       </c>
       <c r="R32" t="n">
-        <v>0.07517874320610389</v>
+        <v>0.07517874320610388</v>
       </c>
       <c r="S32" t="n">
-        <v>0.06955788936105117</v>
+        <v>0.06955788936105121</v>
       </c>
       <c r="T32" t="n">
-        <v>0.07735346069325816</v>
+        <v>0.07735346069325813</v>
       </c>
       <c r="U32" t="n">
-        <v>0.07383690249156895</v>
+        <v>0.07383690249156893</v>
       </c>
       <c r="V32" t="n">
         <v>0.0754319287576212</v>
       </c>
       <c r="W32" t="n">
-        <v>0.07357347481457348</v>
+        <v>0.07357347481457346</v>
       </c>
       <c r="X32" t="n">
-        <v>0.07365888159303023</v>
+        <v>0.07365888159303025</v>
       </c>
     </row>
     <row r="33">
@@ -2930,7 +2930,7 @@
         <v>0.01946380711113172</v>
       </c>
       <c r="T33" t="n">
-        <v>0.01542003171469385</v>
+        <v>0.01542003171469384</v>
       </c>
       <c r="U33" t="n">
         <v>0.01633563845895213</v>
@@ -2939,7 +2939,7 @@
         <v>0.01580269133331256</v>
       </c>
       <c r="W33" t="n">
-        <v>0.0159288558455558</v>
+        <v>0.01592885584555581</v>
       </c>
       <c r="X33" t="n">
         <v>0.01807337799939585</v>
@@ -2967,7 +2967,7 @@
         <v>0.00218893541759769</v>
       </c>
       <c r="G34" t="n">
-        <v>0.002031986675284236</v>
+        <v>0.002031986675284237</v>
       </c>
       <c r="H34" t="n">
         <v>0.002878474880759767</v>
@@ -2979,7 +2979,7 @@
         <v>0.002513863076635936</v>
       </c>
       <c r="K34" t="n">
-        <v>0.002543339226944511</v>
+        <v>0.00254333922694451</v>
       </c>
       <c r="L34" t="n">
         <v>0.002781314889274042</v>
@@ -2991,10 +2991,10 @@
         <v>0.002556621523983847</v>
       </c>
       <c r="O34" t="n">
-        <v>0.002357951397727977</v>
+        <v>0.002357951397727976</v>
       </c>
       <c r="P34" t="n">
-        <v>0.002753235513134262</v>
+        <v>0.002753235513134261</v>
       </c>
       <c r="Q34" t="n">
         <v>0.00169546529376626</v>
@@ -3015,7 +3015,7 @@
         <v>0.00165906755693273</v>
       </c>
       <c r="W34" t="n">
-        <v>0.001553238839197378</v>
+        <v>0.001553238839197379</v>
       </c>
       <c r="X34" t="n">
         <v>0.001691792594094028</v>
@@ -3031,7 +3031,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>0.001700261962976582</v>
+        <v>0.001700261962976581</v>
       </c>
       <c r="D35" t="n">
         <v>0.00146279177419494</v>
@@ -3116,13 +3116,13 @@
         <v>0.002000341140176281</v>
       </c>
       <c r="F36" t="n">
-        <v>0.002097120727649401</v>
+        <v>0.0020971207276494</v>
       </c>
       <c r="G36" t="n">
         <v>0.001981072882440781</v>
       </c>
       <c r="H36" t="n">
-        <v>0.002293916438563828</v>
+        <v>0.002293916438563829</v>
       </c>
       <c r="I36" t="n">
         <v>0.002386187128420586</v>
@@ -3140,7 +3140,7 @@
         <v>0.002599946184093514</v>
       </c>
       <c r="N36" t="n">
-        <v>0.002613301619363763</v>
+        <v>0.002613301619363764</v>
       </c>
       <c r="O36" t="n">
         <v>0.002407282112388223</v>
@@ -3152,19 +3152,19 @@
         <v>0.003024632627132223</v>
       </c>
       <c r="R36" t="n">
-        <v>0.002945652008935636</v>
+        <v>0.002945652008935635</v>
       </c>
       <c r="S36" t="n">
         <v>0.003012034613241722</v>
       </c>
       <c r="T36" t="n">
-        <v>0.004439068267849612</v>
+        <v>0.004439068267849614</v>
       </c>
       <c r="U36" t="n">
         <v>0.003608136284385434</v>
       </c>
       <c r="V36" t="n">
-        <v>0.004246981452791832</v>
+        <v>0.004246981452791831</v>
       </c>
       <c r="W36" t="n">
         <v>0.002858405271592424</v>
@@ -3183,13 +3183,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>0.01295219084710018</v>
+        <v>0.01295219084710019</v>
       </c>
       <c r="D37" t="n">
-        <v>0.01149667718995707</v>
+        <v>0.01149667718995706</v>
       </c>
       <c r="E37" t="n">
-        <v>0.01251534087582464</v>
+        <v>0.01251534087582465</v>
       </c>
       <c r="F37" t="n">
         <v>0.01141222194447285</v>
@@ -3204,7 +3204,7 @@
         <v>0.01137388804176815</v>
       </c>
       <c r="J37" t="n">
-        <v>0.01148536174570583</v>
+        <v>0.01148536174570582</v>
       </c>
       <c r="K37" t="n">
         <v>0.01198769156619319</v>
@@ -3219,16 +3219,16 @@
         <v>0.01859055754639198</v>
       </c>
       <c r="O37" t="n">
-        <v>0.01711763812846321</v>
+        <v>0.0171176381284632</v>
       </c>
       <c r="P37" t="n">
         <v>0.01469427072133571</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.01587918674893038</v>
+        <v>0.01587918674893039</v>
       </c>
       <c r="R37" t="n">
-        <v>0.016183420699122</v>
+        <v>0.01618342069912198</v>
       </c>
       <c r="S37" t="n">
         <v>0.01568561756053418</v>
@@ -3243,7 +3243,7 @@
         <v>0.01250438766124125</v>
       </c>
       <c r="W37" t="n">
-        <v>0.01542141165105377</v>
+        <v>0.01542141165105378</v>
       </c>
       <c r="X37" t="n">
         <v>0.01575451406367784</v>
@@ -3304,7 +3304,7 @@
         <v>0.001564994563774509</v>
       </c>
       <c r="R38" t="n">
-        <v>0.00142264011310059</v>
+        <v>0.001422640113100591</v>
       </c>
       <c r="S38" t="n">
         <v>0.001368212917573547</v>
@@ -3377,7 +3377,7 @@
         <v>0.0008746057285568903</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0007730913510188379</v>
+        <v>0.000773091351018838</v>
       </c>
       <c r="R39" t="n">
         <v>0.0007031290281968922</v>
@@ -3386,7 +3386,7 @@
         <v>0.0006762789428006587</v>
       </c>
       <c r="T39" t="n">
-        <v>0.0008047363064814313</v>
+        <v>0.0008047363064814311</v>
       </c>
       <c r="U39" t="n">
         <v>0.0007364211140901281</v>
@@ -3395,7 +3395,7 @@
         <v>0.0008217832042097023</v>
       </c>
       <c r="W39" t="n">
-        <v>0.0007574343225275792</v>
+        <v>0.0007574343225275791</v>
       </c>
       <c r="X39" t="n">
         <v>0.0008442240634035798</v>
@@ -3411,13 +3411,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>0.0005922329884014507</v>
+        <v>0.0005922329884014506</v>
       </c>
       <c r="D40" t="n">
         <v>0.0003390958827799472</v>
       </c>
       <c r="E40" t="n">
-        <v>0.0004951012248443945</v>
+        <v>0.0004951012248443944</v>
       </c>
       <c r="F40" t="n">
         <v>0.0004198842133221775</v>
@@ -3450,13 +3450,13 @@
         <v>0.0004899771508899769</v>
       </c>
       <c r="P40" t="n">
-        <v>0.0005697843412934421</v>
+        <v>0.000569784341293442</v>
       </c>
       <c r="Q40" t="n">
         <v>0.0004527358870421008</v>
       </c>
       <c r="R40" t="n">
-        <v>0.0004331484389608432</v>
+        <v>0.0004331484389608433</v>
       </c>
       <c r="S40" t="n">
         <v>0.0004376806583883769</v>
@@ -3502,7 +3502,7 @@
         <v>0.001677838859884845</v>
       </c>
       <c r="H41" t="n">
-        <v>0.001798981078616495</v>
+        <v>0.001798981078616494</v>
       </c>
       <c r="I41" t="n">
         <v>0.001977530980986313</v>
@@ -3514,7 +3514,7 @@
         <v>0.001771807007828757</v>
       </c>
       <c r="L41" t="n">
-        <v>0.001727970768783272</v>
+        <v>0.001727970768783273</v>
       </c>
       <c r="M41" t="n">
         <v>0.001733581124365608</v>
@@ -3547,7 +3547,7 @@
         <v>0.001434604549387589</v>
       </c>
       <c r="W41" t="n">
-        <v>0.001392555601643226</v>
+        <v>0.001392555601643227</v>
       </c>
       <c r="X41" t="n">
         <v>0.001514474493975027</v>
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.0006536504337314602</v>
+        <v>0.0006536504337314601</v>
       </c>
       <c r="D42" t="n">
         <v>0.0005122625019390189</v>
       </c>
       <c r="E42" t="n">
-        <v>0.0007009730351209191</v>
+        <v>0.0007009730351209193</v>
       </c>
       <c r="F42" t="n">
         <v>0.0005366578890962948</v>
@@ -3593,13 +3593,13 @@
         <v>0.0005754775590126174</v>
       </c>
       <c r="M42" t="n">
-        <v>0.0005869570019070297</v>
+        <v>0.0005869570019070296</v>
       </c>
       <c r="N42" t="n">
         <v>0.000554257943599482</v>
       </c>
       <c r="O42" t="n">
-        <v>0.000527325751104266</v>
+        <v>0.0005273257511042661</v>
       </c>
       <c r="P42" t="n">
         <v>0.0006552409192226835</v>
@@ -3660,13 +3660,13 @@
         <v>0.001870494574138616</v>
       </c>
       <c r="J43" t="n">
-        <v>0.002201474033431801</v>
+        <v>0.002201474033431802</v>
       </c>
       <c r="K43" t="n">
         <v>0.002298961116032607</v>
       </c>
       <c r="L43" t="n">
-        <v>0.002160930714918154</v>
+        <v>0.002160930714918153</v>
       </c>
       <c r="M43" t="n">
         <v>0.002320685608933561</v>
@@ -3678,10 +3678,10 @@
         <v>0.00232716964706382</v>
       </c>
       <c r="P43" t="n">
-        <v>0.003057545042663302</v>
+        <v>0.003057545042663301</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.001849011924785596</v>
+        <v>0.001849011924785595</v>
       </c>
       <c r="R43" t="n">
         <v>0.001772709336889924</v>
@@ -3715,46 +3715,46 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>0.008051677136266562</v>
+        <v>0.008051677136266557</v>
       </c>
       <c r="D44" t="n">
-        <v>0.005796888556598212</v>
+        <v>0.005796888556598213</v>
       </c>
       <c r="E44" t="n">
-        <v>0.006681141987196524</v>
+        <v>0.006681141987196526</v>
       </c>
       <c r="F44" t="n">
-        <v>0.006718383473457041</v>
+        <v>0.006718383473457038</v>
       </c>
       <c r="G44" t="n">
-        <v>0.006532127469918682</v>
+        <v>0.006532127469918681</v>
       </c>
       <c r="H44" t="n">
-        <v>0.007172925516126357</v>
+        <v>0.007172925516126356</v>
       </c>
       <c r="I44" t="n">
-        <v>0.00798464285059345</v>
+        <v>0.007984642850593448</v>
       </c>
       <c r="J44" t="n">
-        <v>0.007912028610556421</v>
+        <v>0.007912028610556423</v>
       </c>
       <c r="K44" t="n">
-        <v>0.007629111395099523</v>
+        <v>0.007629111395099524</v>
       </c>
       <c r="L44" t="n">
-        <v>0.007237817148233793</v>
+        <v>0.007237817148233795</v>
       </c>
       <c r="M44" t="n">
-        <v>0.007593651943283483</v>
+        <v>0.007593651943283486</v>
       </c>
       <c r="N44" t="n">
-        <v>0.00726600643773464</v>
+        <v>0.007266006437734643</v>
       </c>
       <c r="O44" t="n">
         <v>0.00762578464648082</v>
       </c>
       <c r="P44" t="n">
-        <v>0.007568876168917955</v>
+        <v>0.007568876168917953</v>
       </c>
       <c r="Q44" t="n">
         <v>0.005947137003746716</v>
@@ -3769,16 +3769,16 @@
         <v>0.005848659298972794</v>
       </c>
       <c r="U44" t="n">
-        <v>0.005737025412306784</v>
+        <v>0.005737025412306786</v>
       </c>
       <c r="V44" t="n">
-        <v>0.005780156307359079</v>
+        <v>0.005780156307359078</v>
       </c>
       <c r="W44" t="n">
         <v>0.005467182217599315</v>
       </c>
       <c r="X44" t="n">
-        <v>0.005709338407188634</v>
+        <v>0.005709338407188636</v>
       </c>
     </row>
     <row r="45">
@@ -3827,7 +3827,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>0.0003928986989058053</v>
+        <v>0.0003928986989058052</v>
       </c>
       <c r="D46" t="n">
         <v>0.0001652679279483035</v>
@@ -3866,7 +3866,7 @@
         <v>0.0001222442710285827</v>
       </c>
       <c r="P46" t="n">
-        <v>0.0002959610545892669</v>
+        <v>0.000295961054589267</v>
       </c>
       <c r="Q46" t="n">
         <v>0.0001291276904807788</v>
@@ -3927,7 +3927,7 @@
         <v>0.001222035271777637</v>
       </c>
       <c r="K47" t="n">
-        <v>0.001175702139708708</v>
+        <v>0.001175702139708707</v>
       </c>
       <c r="L47" t="n">
         <v>0.0009436700621497391</v>
@@ -3948,13 +3948,13 @@
         <v>0.0008995313109227733</v>
       </c>
       <c r="R47" t="n">
-        <v>0.0008894953739191462</v>
+        <v>0.0008894953739191461</v>
       </c>
       <c r="S47" t="n">
-        <v>0.0008062596501979746</v>
+        <v>0.0008062596501979747</v>
       </c>
       <c r="T47" t="n">
-        <v>0.0007940797158799245</v>
+        <v>0.0007940797158799244</v>
       </c>
       <c r="U47" t="n">
         <v>0.0007457157113196061</v>
@@ -3982,7 +3982,7 @@
         <v>0.002922920305477617</v>
       </c>
       <c r="D48" t="n">
-        <v>0.003118158256666015</v>
+        <v>0.003118158256666016</v>
       </c>
       <c r="E48" t="n">
         <v>0.002102155648227394</v>
@@ -3991,7 +3991,7 @@
         <v>0.002000857921979479</v>
       </c>
       <c r="G48" t="n">
-        <v>0.001757820914272071</v>
+        <v>0.001757820914272072</v>
       </c>
       <c r="H48" t="n">
         <v>0.006856393821210597</v>
@@ -4000,16 +4000,16 @@
         <v>0.002770312393596219</v>
       </c>
       <c r="J48" t="n">
-        <v>0.002668550297835455</v>
+        <v>0.002668550297835454</v>
       </c>
       <c r="K48" t="n">
         <v>0.002339439014073745</v>
       </c>
       <c r="L48" t="n">
-        <v>0.00477287533858553</v>
+        <v>0.004772875338585529</v>
       </c>
       <c r="M48" t="n">
-        <v>0.004088464401272148</v>
+        <v>0.004088464401272147</v>
       </c>
       <c r="N48" t="n">
         <v>0.00318436380173693</v>
@@ -4018,7 +4018,7 @@
         <v>0.002575058146735458</v>
       </c>
       <c r="P48" t="n">
-        <v>0.001939905940590897</v>
+        <v>0.001939905940590896</v>
       </c>
       <c r="Q48" t="n">
         <v>0.001061511804645654</v>
@@ -4073,13 +4073,13 @@
         <v>0.001602937644267719</v>
       </c>
       <c r="I49" t="n">
-        <v>0.002005229813738028</v>
+        <v>0.002005229813738029</v>
       </c>
       <c r="J49" t="n">
         <v>0.001723250986677346</v>
       </c>
       <c r="K49" t="n">
-        <v>0.00143385818905617</v>
+        <v>0.001433858189056169</v>
       </c>
       <c r="L49" t="n">
         <v>0.001494597893364903</v>
@@ -4118,7 +4118,7 @@
         <v>0.001375758082311067</v>
       </c>
       <c r="X49" t="n">
-        <v>0.001027811295447068</v>
+        <v>0.001027811295447069</v>
       </c>
     </row>
     <row r="50">
@@ -4137,7 +4137,7 @@
         <v>0.0008488402841893652</v>
       </c>
       <c r="E50" t="n">
-        <v>0.001261473008205696</v>
+        <v>0.001261473008205695</v>
       </c>
       <c r="F50" t="n">
         <v>0.00116570371189183</v>
@@ -4173,7 +4173,7 @@
         <v>0.002025410160941475</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.002059937905413471</v>
+        <v>0.00205993790541347</v>
       </c>
       <c r="R50" t="n">
         <v>0.001820178079017134</v>
@@ -4185,7 +4185,7 @@
         <v>0.001771144433077264</v>
       </c>
       <c r="U50" t="n">
-        <v>0.001863253738734104</v>
+        <v>0.001863253738734103</v>
       </c>
       <c r="V50" t="n">
         <v>0.002029596088468575</v>
@@ -4194,7 +4194,7 @@
         <v>0.001865279595055701</v>
       </c>
       <c r="X50" t="n">
-        <v>0.001996310595289773</v>
+        <v>0.001996310595289774</v>
       </c>
     </row>
     <row r="51">
@@ -4207,19 +4207,19 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>0.02919806801979834</v>
+        <v>0.02919806801979833</v>
       </c>
       <c r="D51" t="n">
-        <v>0.01512116272633249</v>
+        <v>0.0151211627263325</v>
       </c>
       <c r="E51" t="n">
         <v>0.01860488574330434</v>
       </c>
       <c r="F51" t="n">
-        <v>0.02537433047024493</v>
+        <v>0.02537433047024494</v>
       </c>
       <c r="G51" t="n">
-        <v>0.02949501266564629</v>
+        <v>0.02949501266564628</v>
       </c>
       <c r="H51" t="n">
         <v>0.01781941077747047</v>
@@ -4234,10 +4234,10 @@
         <v>0.02669370804922982</v>
       </c>
       <c r="L51" t="n">
-        <v>0.02237447408230737</v>
+        <v>0.02237447408230736</v>
       </c>
       <c r="M51" t="n">
-        <v>0.02491903705307994</v>
+        <v>0.02491903705307993</v>
       </c>
       <c r="N51" t="n">
         <v>0.02954064171822608</v>
@@ -4246,16 +4246,16 @@
         <v>0.03045447023635677</v>
       </c>
       <c r="P51" t="n">
-        <v>0.0405413665523235</v>
+        <v>0.04054136655232351</v>
       </c>
       <c r="Q51" t="n">
         <v>0.03850744476475976</v>
       </c>
       <c r="R51" t="n">
-        <v>0.03754494363691104</v>
+        <v>0.03754494363691105</v>
       </c>
       <c r="S51" t="n">
-        <v>0.03055677934588212</v>
+        <v>0.03055677934588211</v>
       </c>
       <c r="T51" t="n">
         <v>0.03328264830221141</v>
@@ -4267,10 +4267,10 @@
         <v>0.03427240898280191</v>
       </c>
       <c r="W51" t="n">
-        <v>0.0347910954141751</v>
+        <v>0.03479109541417512</v>
       </c>
       <c r="X51" t="n">
-        <v>0.03160157891523441</v>
+        <v>0.03160157891523442</v>
       </c>
     </row>
     <row r="52">
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>0.001597207269708889</v>
+        <v>0.00159720726970889</v>
       </c>
       <c r="D52" t="n">
         <v>0.001158567475565708</v>
@@ -4307,13 +4307,13 @@
         <v>0.001475760619721845</v>
       </c>
       <c r="K52" t="n">
-        <v>0.001401134810021687</v>
+        <v>0.001401134810021686</v>
       </c>
       <c r="L52" t="n">
         <v>0.001735493985747702</v>
       </c>
       <c r="M52" t="n">
-        <v>0.001683961894625577</v>
+        <v>0.001683961894625576</v>
       </c>
       <c r="N52" t="n">
         <v>0.001682818672921277</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>0.0004156199374032899</v>
+        <v>0.0004156199374032897</v>
       </c>
       <c r="D53" t="n">
         <v>4.574148194388316e-05</v>
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>0.04852167602884935</v>
+        <v>0.04852167602884937</v>
       </c>
       <c r="D54" t="n">
-        <v>0.0602176051071133</v>
+        <v>0.06021760510711333</v>
       </c>
       <c r="E54" t="n">
-        <v>0.059813813194036</v>
+        <v>0.05981381319403597</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05588676956270584</v>
+        <v>0.05588676956270582</v>
       </c>
       <c r="G54" t="n">
         <v>0.05580535547647238</v>
@@ -4453,7 +4453,7 @@
         <v>0.0594065355682003</v>
       </c>
       <c r="I54" t="n">
-        <v>0.05312948642830605</v>
+        <v>0.05312948642830606</v>
       </c>
       <c r="J54" t="n">
         <v>0.05309861767882104</v>
@@ -4465,25 +4465,25 @@
         <v>0.04660760898529862</v>
       </c>
       <c r="M54" t="n">
-        <v>0.03948793954627903</v>
+        <v>0.03948793954627904</v>
       </c>
       <c r="N54" t="n">
-        <v>0.03608438154349688</v>
+        <v>0.03608438154349687</v>
       </c>
       <c r="O54" t="n">
-        <v>0.03613427012381953</v>
+        <v>0.03613427012381952</v>
       </c>
       <c r="P54" t="n">
-        <v>0.04503109175192752</v>
+        <v>0.04503109175192755</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.04625310683842485</v>
+        <v>0.04625310683842487</v>
       </c>
       <c r="R54" t="n">
         <v>0.04804235683180244</v>
       </c>
       <c r="S54" t="n">
-        <v>0.0502153446124031</v>
+        <v>0.05021534461240311</v>
       </c>
       <c r="T54" t="n">
         <v>0.0474576029361444</v>
@@ -4492,13 +4492,13 @@
         <v>0.04770924973234862</v>
       </c>
       <c r="V54" t="n">
-        <v>0.046536384366485</v>
+        <v>0.04653638436648498</v>
       </c>
       <c r="W54" t="n">
         <v>0.04253108488628986</v>
       </c>
       <c r="X54" t="n">
-        <v>0.04867681646997881</v>
+        <v>0.0486768164699788</v>
       </c>
     </row>
     <row r="55">
@@ -4511,7 +4511,7 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>0.01233616401793564</v>
+        <v>0.01233616401793563</v>
       </c>
       <c r="D55" t="n">
         <v>0.01057455701656512</v>
@@ -4535,7 +4535,7 @@
         <v>0.01371005769676752</v>
       </c>
       <c r="K55" t="n">
-        <v>0.01247843540314506</v>
+        <v>0.01247843540314507</v>
       </c>
       <c r="L55" t="n">
         <v>0.01469684242338833</v>
@@ -4559,7 +4559,7 @@
         <v>0.01168076776488939</v>
       </c>
       <c r="S55" t="n">
-        <v>0.01194782738300254</v>
+        <v>0.01194782738300255</v>
       </c>
       <c r="T55" t="n">
         <v>0.01670670253890735</v>
@@ -4587,13 +4587,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>0.00628517812188699</v>
+        <v>0.006285178121886988</v>
       </c>
       <c r="D56" t="n">
         <v>0.004487274925760567</v>
       </c>
       <c r="E56" t="n">
-        <v>0.005091871068783536</v>
+        <v>0.005091871068783537</v>
       </c>
       <c r="F56" t="n">
         <v>0.005395699639366367</v>
@@ -4602,37 +4602,37 @@
         <v>0.005431489778894934</v>
       </c>
       <c r="H56" t="n">
-        <v>0.005046739722962824</v>
+        <v>0.005046739722962825</v>
       </c>
       <c r="I56" t="n">
-        <v>0.005287409686877947</v>
+        <v>0.005287409686877949</v>
       </c>
       <c r="J56" t="n">
         <v>0.005528132851955882</v>
       </c>
       <c r="K56" t="n">
-        <v>0.005805068336141972</v>
+        <v>0.005805068336141971</v>
       </c>
       <c r="L56" t="n">
-        <v>0.007568635732443705</v>
+        <v>0.007568635732443706</v>
       </c>
       <c r="M56" t="n">
-        <v>0.00866546487338409</v>
+        <v>0.008665464873384088</v>
       </c>
       <c r="N56" t="n">
-        <v>0.00959376792824187</v>
+        <v>0.009593767928241867</v>
       </c>
       <c r="O56" t="n">
-        <v>0.00927020465373676</v>
+        <v>0.009270204653736758</v>
       </c>
       <c r="P56" t="n">
-        <v>0.008018806550546655</v>
+        <v>0.008018806550546657</v>
       </c>
       <c r="Q56" t="n">
         <v>0.008423665466393171</v>
       </c>
       <c r="R56" t="n">
-        <v>0.008647771553838959</v>
+        <v>0.008647771553838956</v>
       </c>
       <c r="S56" t="n">
         <v>0.008503198399954399</v>
@@ -4650,7 +4650,7 @@
         <v>0.009023039590452548</v>
       </c>
       <c r="X56" t="n">
-        <v>0.009324525456474664</v>
+        <v>0.009324525456474667</v>
       </c>
     </row>
     <row r="57">
@@ -4666,7 +4666,7 @@
         <v>0.001622318897065757</v>
       </c>
       <c r="D57" t="n">
-        <v>0.001552312391830396</v>
+        <v>0.001552312391830397</v>
       </c>
       <c r="E57" t="n">
         <v>0.001956557172937346</v>
@@ -4681,7 +4681,7 @@
         <v>0.002070569700751715</v>
       </c>
       <c r="I57" t="n">
-        <v>0.00205646049277945</v>
+        <v>0.002056460492779451</v>
       </c>
       <c r="J57" t="n">
         <v>0.001999173649395711</v>
@@ -4693,7 +4693,7 @@
         <v>0.001767901717650041</v>
       </c>
       <c r="M57" t="n">
-        <v>0.001727088681628018</v>
+        <v>0.001727088681628017</v>
       </c>
       <c r="N57" t="n">
         <v>0.001637811097169144</v>
@@ -4720,7 +4720,7 @@
         <v>0.002046376383304698</v>
       </c>
       <c r="V57" t="n">
-        <v>0.001866923389393311</v>
+        <v>0.001866923389393312</v>
       </c>
       <c r="W57" t="n">
         <v>0.002017703157704348</v>
@@ -4760,7 +4760,7 @@
         <v>0.001386986404170697</v>
       </c>
       <c r="J58" t="n">
-        <v>0.001481948911116927</v>
+        <v>0.001481948911116928</v>
       </c>
       <c r="K58" t="n">
         <v>0.001252701126834043</v>
@@ -4784,7 +4784,7 @@
         <v>0.0002995064481644162</v>
       </c>
       <c r="R58" t="n">
-        <v>0.0003054471115144707</v>
+        <v>0.0003054471115144708</v>
       </c>
       <c r="S58" t="n">
         <v>0.0003108065190751024</v>
@@ -4836,7 +4836,7 @@
         <v>0.001556733127308035</v>
       </c>
       <c r="J59" t="n">
-        <v>0.001885003845512443</v>
+        <v>0.001885003845512442</v>
       </c>
       <c r="K59" t="n">
         <v>0.001708798239590256</v>
@@ -4854,7 +4854,7 @@
         <v>0.001544770907897873</v>
       </c>
       <c r="P59" t="n">
-        <v>0.001590778146586869</v>
+        <v>0.00159077814658687</v>
       </c>
       <c r="Q59" t="n">
         <v>0.001014358666440507</v>
@@ -4869,13 +4869,13 @@
         <v>0.0008944735744596147</v>
       </c>
       <c r="U59" t="n">
-        <v>0.000873491502749461</v>
+        <v>0.0008734915027494611</v>
       </c>
       <c r="V59" t="n">
-        <v>0.0009176794014258088</v>
+        <v>0.0009176794014258091</v>
       </c>
       <c r="W59" t="n">
-        <v>0.0009253341286145719</v>
+        <v>0.0009253341286145718</v>
       </c>
       <c r="X59" t="n">
         <v>0.0009427776961792947</v>
@@ -4918,13 +4918,13 @@
         <v>0.01802070105198976</v>
       </c>
       <c r="L60" t="n">
-        <v>0.01317146963009</v>
+        <v>0.01317146963008999</v>
       </c>
       <c r="M60" t="n">
-        <v>0.01630599429204343</v>
+        <v>0.01630599429204344</v>
       </c>
       <c r="N60" t="n">
-        <v>0.01785841687480033</v>
+        <v>0.01785841687480032</v>
       </c>
       <c r="O60" t="n">
         <v>0.01804600183697185</v>
@@ -4970,7 +4970,7 @@
         <v>0.001029017660264411</v>
       </c>
       <c r="D61" t="n">
-        <v>0.0005871901190528741</v>
+        <v>0.000587190119052874</v>
       </c>
       <c r="E61" t="n">
         <v>0.000609339534804552</v>
@@ -4979,7 +4979,7 @@
         <v>0.000696408903946037</v>
       </c>
       <c r="G61" t="n">
-        <v>0.0006759245136621733</v>
+        <v>0.0006759245136621734</v>
       </c>
       <c r="H61" t="n">
         <v>0.0008877696193038702</v>
@@ -4991,7 +4991,7 @@
         <v>0.0008322885588751784</v>
       </c>
       <c r="K61" t="n">
-        <v>0.0007600953585808023</v>
+        <v>0.0007600953585808022</v>
       </c>
       <c r="L61" t="n">
         <v>0.0006778514154205922</v>
@@ -5006,13 +5006,13 @@
         <v>0.0007319115523615228</v>
       </c>
       <c r="P61" t="n">
-        <v>0.0007334800686729544</v>
+        <v>0.0007334800686729545</v>
       </c>
       <c r="Q61" t="n">
         <v>0.0005712401291744453</v>
       </c>
       <c r="R61" t="n">
-        <v>0.0005373739352383778</v>
+        <v>0.0005373739352383779</v>
       </c>
       <c r="S61" t="n">
         <v>0.0005557684020862621</v>
@@ -5027,7 +5027,7 @@
         <v>0.0005202871553180884</v>
       </c>
       <c r="W61" t="n">
-        <v>0.000553658233339282</v>
+        <v>0.0005536582333392819</v>
       </c>
       <c r="X61" t="n">
         <v>0.0005669382634162059</v>
@@ -5082,7 +5082,7 @@
         <v>1.669565474525113e-05</v>
       </c>
       <c r="P62" t="n">
-        <v>7.853260074394453e-05</v>
+        <v>7.853260074394454e-05</v>
       </c>
       <c r="Q62" t="n">
         <v>1.293861920181191e-05</v>
@@ -5128,34 +5128,34 @@
         <v>0.007306187786984639</v>
       </c>
       <c r="F63" t="n">
-        <v>0.006835299571154927</v>
+        <v>0.006835299571154925</v>
       </c>
       <c r="G63" t="n">
-        <v>0.006723035610616273</v>
+        <v>0.006723035610616275</v>
       </c>
       <c r="H63" t="n">
         <v>0.01397665087203057</v>
       </c>
       <c r="I63" t="n">
-        <v>0.009379500067914917</v>
+        <v>0.009379500067914919</v>
       </c>
       <c r="J63" t="n">
-        <v>0.00878175908670153</v>
+        <v>0.008781759086701528</v>
       </c>
       <c r="K63" t="n">
-        <v>0.007967052486987614</v>
+        <v>0.007967052486987616</v>
       </c>
       <c r="L63" t="n">
-        <v>0.008820932152786967</v>
+        <v>0.008820932152786969</v>
       </c>
       <c r="M63" t="n">
         <v>0.00823281144763895</v>
       </c>
       <c r="N63" t="n">
-        <v>0.008620088721468164</v>
+        <v>0.008620088721468163</v>
       </c>
       <c r="O63" t="n">
-        <v>0.007270356087624188</v>
+        <v>0.007270356087624186</v>
       </c>
       <c r="P63" t="n">
         <v>0.006840023609523023</v>
@@ -5164,7 +5164,7 @@
         <v>0.006516726053691604</v>
       </c>
       <c r="R63" t="n">
-        <v>0.006536714416227574</v>
+        <v>0.006536714416227575</v>
       </c>
       <c r="S63" t="n">
         <v>0.008231217490099132</v>
@@ -5173,10 +5173,10 @@
         <v>0.008233786625261407</v>
       </c>
       <c r="U63" t="n">
-        <v>0.00764753248871793</v>
+        <v>0.007647532488717932</v>
       </c>
       <c r="V63" t="n">
-        <v>0.008109174094025135</v>
+        <v>0.008109174094025137</v>
       </c>
       <c r="W63" t="n">
         <v>0.008980080941962143</v>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>0.0005520709205788847</v>
+        <v>0.0005520709205788846</v>
       </c>
       <c r="D64" t="n">
         <v>0.0002730748612434581</v>
@@ -5210,7 +5210,7 @@
         <v>0.0002947532134775015</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0003270706677032809</v>
+        <v>0.0003270706677032808</v>
       </c>
       <c r="I64" t="n">
         <v>0.000339265590867864</v>
@@ -5271,7 +5271,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>0.02215572488446529</v>
+        <v>0.02215572488446528</v>
       </c>
       <c r="D65" t="n">
         <v>0.01827957820901883</v>
@@ -5283,7 +5283,7 @@
         <v>0.01832988154909587</v>
       </c>
       <c r="G65" t="n">
-        <v>0.0200698694469442</v>
+        <v>0.02006986944694421</v>
       </c>
       <c r="H65" t="n">
         <v>0.02120247162804979</v>
@@ -5292,10 +5292,10 @@
         <v>0.01995274310699094</v>
       </c>
       <c r="J65" t="n">
-        <v>0.01958580893716277</v>
+        <v>0.01958580893716276</v>
       </c>
       <c r="K65" t="n">
-        <v>0.0201794978208279</v>
+        <v>0.02017949782082789</v>
       </c>
       <c r="L65" t="n">
         <v>0.03987217979542444</v>
@@ -5307,7 +5307,7 @@
         <v>0.03373778193917261</v>
       </c>
       <c r="O65" t="n">
-        <v>0.03191635580541908</v>
+        <v>0.03191635580541907</v>
       </c>
       <c r="P65" t="n">
         <v>0.02151594355315971</v>
@@ -5316,10 +5316,10 @@
         <v>0.02381511676213546</v>
       </c>
       <c r="R65" t="n">
-        <v>0.02418152658390422</v>
+        <v>0.02418152658390423</v>
       </c>
       <c r="S65" t="n">
-        <v>0.02483331070056169</v>
+        <v>0.0248333107005617</v>
       </c>
       <c r="T65" t="n">
         <v>0.021966571115191</v>
@@ -5334,7 +5334,7 @@
         <v>0.02517302632706501</v>
       </c>
       <c r="X65" t="n">
-        <v>0.02562648688959676</v>
+        <v>0.02562648688959677</v>
       </c>
     </row>
     <row r="66">
@@ -5404,7 +5404,7 @@
         <v>0.001767261187953529</v>
       </c>
       <c r="V66" t="n">
-        <v>0.001773588723903561</v>
+        <v>0.00177358872390356</v>
       </c>
       <c r="W66" t="n">
         <v>0.001601386420331221</v>
@@ -5499,22 +5499,22 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>0.001044790009409675</v>
+        <v>0.001044790009409676</v>
       </c>
       <c r="D68" t="n">
         <v>0.0005799680202138945</v>
       </c>
       <c r="E68" t="n">
-        <v>0.0006446781942266567</v>
+        <v>0.0006446781942266568</v>
       </c>
       <c r="F68" t="n">
-        <v>0.000562762796826489</v>
+        <v>0.0005627627968264891</v>
       </c>
       <c r="G68" t="n">
-        <v>0.0005311934358098214</v>
+        <v>0.0005311934358098213</v>
       </c>
       <c r="H68" t="n">
-        <v>0.0007217410956356254</v>
+        <v>0.0007217410956356253</v>
       </c>
       <c r="I68" t="n">
         <v>0.0006045143430117832</v>
@@ -5535,19 +5535,19 @@
         <v>0.000718541404793895</v>
       </c>
       <c r="O68" t="n">
-        <v>0.0006438704822011354</v>
+        <v>0.0006438704822011355</v>
       </c>
       <c r="P68" t="n">
-        <v>0.0006694668811964782</v>
+        <v>0.0006694668811964784</v>
       </c>
       <c r="Q68" t="n">
         <v>0.0004218453504751575</v>
       </c>
       <c r="R68" t="n">
-        <v>0.0003930535936588607</v>
+        <v>0.0003930535936588608</v>
       </c>
       <c r="S68" t="n">
-        <v>0.0004212461919284911</v>
+        <v>0.0004212461919284912</v>
       </c>
       <c r="T68" t="n">
         <v>0.000375794128394639</v>
@@ -5559,7 +5559,7 @@
         <v>0.0004064859784102561</v>
       </c>
       <c r="W68" t="n">
-        <v>0.0003578668992158125</v>
+        <v>0.0003578668992158124</v>
       </c>
       <c r="X68" t="n">
         <v>0.0004073051197408604</v>
@@ -5590,7 +5590,7 @@
         <v>0.001057705624729125</v>
       </c>
       <c r="H69" t="n">
-        <v>0.0009111294583740771</v>
+        <v>0.0009111294583740773</v>
       </c>
       <c r="I69" t="n">
         <v>0.001164511594472235</v>
@@ -5599,7 +5599,7 @@
         <v>0.00129551546443772</v>
       </c>
       <c r="K69" t="n">
-        <v>0.001248097381976896</v>
+        <v>0.001248097381976897</v>
       </c>
       <c r="L69" t="n">
         <v>0.001036275422161211</v>
@@ -5611,10 +5611,10 @@
         <v>0.001249900224632599</v>
       </c>
       <c r="O69" t="n">
-        <v>0.001271714183092546</v>
+        <v>0.001271714183092545</v>
       </c>
       <c r="P69" t="n">
-        <v>0.0009753065395922974</v>
+        <v>0.0009753065395922972</v>
       </c>
       <c r="Q69" t="n">
         <v>0.0009835346433855038</v>
@@ -5690,7 +5690,7 @@
         <v>0.0002100533887287226</v>
       </c>
       <c r="P70" t="n">
-        <v>0.0001479070817034301</v>
+        <v>0.00014790708170343</v>
       </c>
       <c r="Q70" t="n">
         <v>9.857986736097504e-05</v>
@@ -5730,16 +5730,16 @@
         <v>0.01175961493199026</v>
       </c>
       <c r="D71" t="n">
-        <v>0.008866285150750544</v>
+        <v>0.008866285150750542</v>
       </c>
       <c r="E71" t="n">
         <v>0.007214451468483784</v>
       </c>
       <c r="F71" t="n">
-        <v>0.009198871414524943</v>
+        <v>0.009198871414524941</v>
       </c>
       <c r="G71" t="n">
-        <v>0.01302423356854713</v>
+        <v>0.01302423356854714</v>
       </c>
       <c r="H71" t="n">
         <v>0.01250032910930332</v>
@@ -5760,25 +5760,25 @@
         <v>0.01453962377111193</v>
       </c>
       <c r="N71" t="n">
-        <v>0.01465818417426094</v>
+        <v>0.01465818417426093</v>
       </c>
       <c r="O71" t="n">
         <v>0.0146277025495812</v>
       </c>
       <c r="P71" t="n">
-        <v>0.00948499020962147</v>
+        <v>0.009484990209621468</v>
       </c>
       <c r="Q71" t="n">
-        <v>0.009891248075217287</v>
+        <v>0.009891248075217289</v>
       </c>
       <c r="R71" t="n">
-        <v>0.0100910579325703</v>
+        <v>0.01009105793257029</v>
       </c>
       <c r="S71" t="n">
-        <v>0.01183010762590309</v>
+        <v>0.01183010762590308</v>
       </c>
       <c r="T71" t="n">
-        <v>0.01530215396257962</v>
+        <v>0.01530215396257961</v>
       </c>
       <c r="U71" t="n">
         <v>0.01155313598464383</v>
@@ -5824,7 +5824,7 @@
         <v>0.00362502829830432</v>
       </c>
       <c r="J72" t="n">
-        <v>0.003365888464202907</v>
+        <v>0.003365888464202906</v>
       </c>
       <c r="K72" t="n">
         <v>0.003145200087188409</v>
@@ -5863,7 +5863,7 @@
         <v>0.003167182818875192</v>
       </c>
       <c r="W72" t="n">
-        <v>0.003227465713831109</v>
+        <v>0.00322746571383111</v>
       </c>
       <c r="X72" t="n">
         <v>0.003936404057034823</v>
@@ -5879,7 +5879,7 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>0.004178183339328882</v>
+        <v>0.004178183339328884</v>
       </c>
       <c r="D73" t="n">
         <v>0.003338264395347859</v>
@@ -5900,46 +5900,46 @@
         <v>0.004009597563296762</v>
       </c>
       <c r="J73" t="n">
-        <v>0.003915908572497794</v>
+        <v>0.003915908572497793</v>
       </c>
       <c r="K73" t="n">
         <v>0.003872701044663123</v>
       </c>
       <c r="L73" t="n">
-        <v>0.006066161559257688</v>
+        <v>0.006066161559257687</v>
       </c>
       <c r="M73" t="n">
-        <v>0.005523398425814044</v>
+        <v>0.005523398425814046</v>
       </c>
       <c r="N73" t="n">
         <v>0.004809267410980415</v>
       </c>
       <c r="O73" t="n">
-        <v>0.004426338653121824</v>
+        <v>0.004426338653121825</v>
       </c>
       <c r="P73" t="n">
-        <v>0.003140180694026949</v>
+        <v>0.003140180694026948</v>
       </c>
       <c r="Q73" t="n">
         <v>0.002902097829053641</v>
       </c>
       <c r="R73" t="n">
-        <v>0.002879238984116776</v>
+        <v>0.002879238984116775</v>
       </c>
       <c r="S73" t="n">
-        <v>0.003202605864862998</v>
+        <v>0.003202605864862999</v>
       </c>
       <c r="T73" t="n">
-        <v>0.00269029372196149</v>
+        <v>0.002690293721961491</v>
       </c>
       <c r="U73" t="n">
         <v>0.002782327928130007</v>
       </c>
       <c r="V73" t="n">
-        <v>0.002753034088385631</v>
+        <v>0.00275303408838563</v>
       </c>
       <c r="W73" t="n">
-        <v>0.002907464955455977</v>
+        <v>0.002907464955455976</v>
       </c>
       <c r="X73" t="n">
         <v>0.003171367947397571</v>
@@ -5967,10 +5967,10 @@
         <v>0.004626631883403981</v>
       </c>
       <c r="G74" t="n">
-        <v>0.004605453107691293</v>
+        <v>0.004605453107691292</v>
       </c>
       <c r="H74" t="n">
-        <v>0.004210533939104602</v>
+        <v>0.004210533939104603</v>
       </c>
       <c r="I74" t="n">
         <v>0.00490713660958841</v>
@@ -5979,16 +5979,16 @@
         <v>0.004751873036131124</v>
       </c>
       <c r="K74" t="n">
-        <v>0.00485283439899844</v>
+        <v>0.004852834398998441</v>
       </c>
       <c r="L74" t="n">
-        <v>0.004649952192338169</v>
+        <v>0.004649952192338168</v>
       </c>
       <c r="M74" t="n">
         <v>0.00494761562359559</v>
       </c>
       <c r="N74" t="n">
-        <v>0.005232034956455194</v>
+        <v>0.005232034956455193</v>
       </c>
       <c r="O74" t="n">
         <v>0.005157560543661918</v>
@@ -5997,7 +5997,7 @@
         <v>0.005006070007571755</v>
       </c>
       <c r="Q74" t="n">
-        <v>0.005828122813845612</v>
+        <v>0.005828122813845611</v>
       </c>
       <c r="R74" t="n">
         <v>0.00566950793542023</v>
@@ -6006,19 +6006,19 @@
         <v>0.00532138905877263</v>
       </c>
       <c r="T74" t="n">
-        <v>0.005212805841532117</v>
+        <v>0.005212805841532116</v>
       </c>
       <c r="U74" t="n">
-        <v>0.005350933362148469</v>
+        <v>0.005350933362148468</v>
       </c>
       <c r="V74" t="n">
         <v>0.00536574652577827</v>
       </c>
       <c r="W74" t="n">
-        <v>0.00525209455200322</v>
+        <v>0.005252094552003219</v>
       </c>
       <c r="X74" t="n">
-        <v>0.005247646391006307</v>
+        <v>0.005247646391006306</v>
       </c>
     </row>
     <row r="75">
@@ -6070,7 +6070,7 @@
         <v>0.0001302249429316326</v>
       </c>
       <c r="P75" t="n">
-        <v>0.0001581159065338492</v>
+        <v>0.0001581159065338491</v>
       </c>
       <c r="Q75" t="n">
         <v>2.249157306246484e-05</v>
@@ -6110,7 +6110,7 @@
         <v>0.002381069842222219</v>
       </c>
       <c r="D76" t="n">
-        <v>0.002069372940958155</v>
+        <v>0.002069372940958154</v>
       </c>
       <c r="E76" t="n">
         <v>0.002361114352333257</v>
@@ -6140,10 +6140,10 @@
         <v>0.002640021627371182</v>
       </c>
       <c r="N76" t="n">
-        <v>0.002488361589262326</v>
+        <v>0.002488361589262327</v>
       </c>
       <c r="O76" t="n">
-        <v>0.002328256523346358</v>
+        <v>0.002328256523346359</v>
       </c>
       <c r="P76" t="n">
         <v>0.00228062986095244</v>
@@ -6161,7 +6161,7 @@
         <v>0.0028266443061852</v>
       </c>
       <c r="U76" t="n">
-        <v>0.002576583434472186</v>
+        <v>0.002576583434472185</v>
       </c>
       <c r="V76" t="n">
         <v>0.002722860620638015</v>
@@ -6222,7 +6222,7 @@
         <v>0.000419654098256628</v>
       </c>
       <c r="P77" t="n">
-        <v>0.0006767370230041173</v>
+        <v>0.0006767370230041171</v>
       </c>
       <c r="Q77" t="n">
         <v>0.0006233248233142055</v>
@@ -6434,7 +6434,7 @@
         <v>0.0005374258061995511</v>
       </c>
       <c r="P80" t="n">
-        <v>0.0005163944706535536</v>
+        <v>0.0005163944706535534</v>
       </c>
       <c r="Q80" t="n">
         <v>0.0004645140534132526</v>
@@ -6471,7 +6471,7 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>0.0003100579280206838</v>
+        <v>0.0003100579280206839</v>
       </c>
       <c r="D81" t="n">
         <v>1.350663460018306e-05</v>
@@ -6589,7 +6589,7 @@
         <v>0.0001384616508503464</v>
       </c>
       <c r="Q82" t="n">
-        <v>0.0001547864939113114</v>
+        <v>0.0001547864939113115</v>
       </c>
       <c r="R82" t="n">
         <v>0.0001433262633120383</v>
@@ -6610,7 +6610,7 @@
         <v>0.0001599299292411345</v>
       </c>
       <c r="X82" t="n">
-        <v>0.0001703428106130727</v>
+        <v>0.0001703428106130726</v>
       </c>
     </row>
     <row r="83">
@@ -6623,16 +6623,16 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>0.008701638195633589</v>
+        <v>0.008701638195633587</v>
       </c>
       <c r="D83" t="n">
         <v>0.007990966373710081</v>
       </c>
       <c r="E83" t="n">
-        <v>0.009612963355679955</v>
+        <v>0.009612963355679951</v>
       </c>
       <c r="F83" t="n">
-        <v>0.009604058135837411</v>
+        <v>0.009604058135837409</v>
       </c>
       <c r="G83" t="n">
         <v>0.009408195530513063</v>
@@ -6653,7 +6653,7 @@
         <v>0.007660188392971399</v>
       </c>
       <c r="M83" t="n">
-        <v>0.008495950100147759</v>
+        <v>0.008495950100147762</v>
       </c>
       <c r="N83" t="n">
         <v>0.009080452548555842</v>
@@ -6665,7 +6665,7 @@
         <v>0.006045155874869821</v>
       </c>
       <c r="Q83" t="n">
-        <v>0.007096799282551346</v>
+        <v>0.007096799282551345</v>
       </c>
       <c r="R83" t="n">
         <v>0.007169294173505002</v>
@@ -6677,16 +6677,16 @@
         <v>0.006861530843150484</v>
       </c>
       <c r="U83" t="n">
-        <v>0.007005429504079843</v>
+        <v>0.007005429504079844</v>
       </c>
       <c r="V83" t="n">
-        <v>0.00706322410913955</v>
+        <v>0.007063224109139549</v>
       </c>
       <c r="W83" t="n">
         <v>0.006115825401708473</v>
       </c>
       <c r="X83" t="n">
-        <v>0.005634945377792915</v>
+        <v>0.005634945377792914</v>
       </c>
     </row>
     <row r="84">
@@ -6708,7 +6708,7 @@
         <v>0.00351895252639183</v>
       </c>
       <c r="F84" t="n">
-        <v>0.003256085244986688</v>
+        <v>0.003256085244986687</v>
       </c>
       <c r="G84" t="n">
         <v>0.003260844092995406</v>
@@ -6723,7 +6723,7 @@
         <v>0.003977140887387745</v>
       </c>
       <c r="K84" t="n">
-        <v>0.003987018253772146</v>
+        <v>0.003987018253772145</v>
       </c>
       <c r="L84" t="n">
         <v>0.002537584136005483</v>
@@ -6747,7 +6747,7 @@
         <v>0.002830984149320935</v>
       </c>
       <c r="S84" t="n">
-        <v>0.002341613384199862</v>
+        <v>0.002341613384199863</v>
       </c>
       <c r="T84" t="n">
         <v>0.00270274398354115</v>
@@ -6814,7 +6814,7 @@
         <v>0.0002696830523382034</v>
       </c>
       <c r="P85" t="n">
-        <v>0.0003059327238425401</v>
+        <v>0.00030593272384254</v>
       </c>
       <c r="Q85" t="inlineStr"/>
       <c r="R85" t="inlineStr"/>
@@ -6850,7 +6850,7 @@
         <v>0.0008960068156742203</v>
       </c>
       <c r="H86" t="n">
-        <v>0.001329225384203489</v>
+        <v>0.001329225384203488</v>
       </c>
       <c r="I86" t="n">
         <v>0.001226369341715373</v>
@@ -6877,13 +6877,13 @@
         <v>0.0009822667685679171</v>
       </c>
       <c r="Q86" t="n">
-        <v>0.0008832527440438467</v>
+        <v>0.0008832527440438466</v>
       </c>
       <c r="R86" t="n">
         <v>0.0007827101878530966</v>
       </c>
       <c r="S86" t="n">
-        <v>0.0007949839131050061</v>
+        <v>0.000794983913105006</v>
       </c>
       <c r="T86" t="n">
         <v>0.000734266518140218</v>
@@ -6990,7 +6990,7 @@
         <v>0.004845582422345934</v>
       </c>
       <c r="D88" t="n">
-        <v>0.002202029378167107</v>
+        <v>0.002202029378167106</v>
       </c>
       <c r="E88" t="n">
         <v>0.001522333088263941</v>
@@ -7011,10 +7011,10 @@
         <v>0.01152228590603828</v>
       </c>
       <c r="K88" t="n">
-        <v>0.00884654056371984</v>
+        <v>0.008846540563719842</v>
       </c>
       <c r="L88" t="n">
-        <v>0.003549647063224264</v>
+        <v>0.003549647063224265</v>
       </c>
       <c r="M88" t="n">
         <v>0.003320961758330834</v>
@@ -7035,7 +7035,7 @@
         <v>0.001143581571528233</v>
       </c>
       <c r="S88" t="n">
-        <v>0.001337794177391911</v>
+        <v>0.001337794177391912</v>
       </c>
       <c r="T88" t="n">
         <v>0.001237449411031378</v>
@@ -7063,7 +7063,7 @@
         </is>
       </c>
       <c r="C89" t="n">
-        <v>8.431379774624418e-05</v>
+        <v>8.431379774624416e-05</v>
       </c>
       <c r="D89" t="inlineStr"/>
       <c r="E89" t="inlineStr"/>
@@ -7102,10 +7102,10 @@
         <v>0.001492078843721803</v>
       </c>
       <c r="D90" t="n">
-        <v>0.001476472219121154</v>
+        <v>0.001476472219121155</v>
       </c>
       <c r="E90" t="n">
-        <v>0.00186021386024007</v>
+        <v>0.001860213860240069</v>
       </c>
       <c r="F90" t="n">
         <v>0.001535828710551069</v>
@@ -7114,7 +7114,7 @@
         <v>0.001494026901975178</v>
       </c>
       <c r="H90" t="n">
-        <v>0.001983746253207404</v>
+        <v>0.001983746253207405</v>
       </c>
       <c r="I90" t="n">
         <v>0.001943973297653785</v>
@@ -7272,10 +7272,10 @@
         <v>0.0005354182492101203</v>
       </c>
       <c r="R92" t="n">
-        <v>0.0004891024831621062</v>
+        <v>0.0004891024831621063</v>
       </c>
       <c r="S92" t="n">
-        <v>0.0005023062578039932</v>
+        <v>0.0005023062578039933</v>
       </c>
       <c r="T92" t="n">
         <v>0.0006447876703936509</v>
@@ -7290,7 +7290,7 @@
         <v>0.0005230722392000048</v>
       </c>
       <c r="X92" t="n">
-        <v>0.0005453908043772664</v>
+        <v>0.0005453908043772665</v>
       </c>
     </row>
     <row r="93">
@@ -7315,10 +7315,10 @@
         <v>0.002628200479865502</v>
       </c>
       <c r="G93" t="n">
-        <v>0.002569687309405898</v>
+        <v>0.002569687309405897</v>
       </c>
       <c r="H93" t="n">
-        <v>0.003874213097958626</v>
+        <v>0.003874213097958625</v>
       </c>
       <c r="I93" t="n">
         <v>0.002966708597470477</v>
@@ -7379,7 +7379,7 @@
         </is>
       </c>
       <c r="C94" t="n">
-        <v>0.0002813250921807388</v>
+        <v>0.0002813250921807387</v>
       </c>
       <c r="D94" t="n">
         <v>0.0001098474127627847</v>
@@ -7394,7 +7394,7 @@
         <v>0.0001084207581254606</v>
       </c>
       <c r="H94" t="n">
-        <v>0.0001375603705838404</v>
+        <v>0.0001375603705838403</v>
       </c>
       <c r="I94" t="n">
         <v>0.0001189230860733847</v>
@@ -7412,7 +7412,7 @@
         <v>0.000202823294776038</v>
       </c>
       <c r="N94" t="n">
-        <v>0.0001560080731815223</v>
+        <v>0.0001560080731815222</v>
       </c>
       <c r="O94" t="n">
         <v>0.0001351952643252284</v>
@@ -7430,7 +7430,7 @@
         <v>0.0001362444544378987</v>
       </c>
       <c r="T94" t="n">
-        <v>0.0001369788901956179</v>
+        <v>0.000136978890195618</v>
       </c>
       <c r="U94" t="n">
         <v>0.0001086242477420289</v>
@@ -7464,7 +7464,7 @@
         <v>0.0004049141035098167</v>
       </c>
       <c r="F95" t="n">
-        <v>0.0003487468423779967</v>
+        <v>0.0003487468423779968</v>
       </c>
       <c r="G95" t="n">
         <v>0.0003322191324536162</v>
@@ -7482,28 +7482,28 @@
         <v>0.0004106089571882278</v>
       </c>
       <c r="L95" t="n">
-        <v>0.000888742571615771</v>
+        <v>0.0008887425716157709</v>
       </c>
       <c r="M95" t="n">
         <v>0.0007397873408785618</v>
       </c>
       <c r="N95" t="n">
-        <v>0.0005463397459712021</v>
+        <v>0.0005463397459712022</v>
       </c>
       <c r="O95" t="n">
         <v>0.0005096888826338456</v>
       </c>
       <c r="P95" t="n">
-        <v>0.0003056326914082239</v>
+        <v>0.0003056326914082238</v>
       </c>
       <c r="Q95" t="n">
-        <v>0.0003232501890592899</v>
+        <v>0.00032325018905929</v>
       </c>
       <c r="R95" t="n">
-        <v>0.0003202019188374515</v>
+        <v>0.0003202019188374516</v>
       </c>
       <c r="S95" t="n">
-        <v>0.0003917097653852718</v>
+        <v>0.0003917097653852717</v>
       </c>
       <c r="T95" t="n">
         <v>0.0004120372200429204</v>
@@ -7512,7 +7512,7 @@
         <v>0.0003307763779355317</v>
       </c>
       <c r="V95" t="n">
-        <v>0.0003382137291365939</v>
+        <v>0.0003382137291365938</v>
       </c>
       <c r="W95" t="n">
         <v>0.0003575714488199367</v>
@@ -7582,7 +7582,7 @@
         <v>0.002138120470615271</v>
       </c>
       <c r="T96" t="n">
-        <v>0.002205368064259097</v>
+        <v>0.002205368064259098</v>
       </c>
       <c r="U96" t="n">
         <v>0.002177134160511849</v>
@@ -7591,7 +7591,7 @@
         <v>0.002190928183943489</v>
       </c>
       <c r="W96" t="n">
-        <v>0.001853781541449552</v>
+        <v>0.001853781541449553</v>
       </c>
       <c r="X96" t="n">
         <v>0.001900170119180276</v>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="C97" t="n">
-        <v>0.0001298476747648489</v>
+        <v>0.000129847674764849</v>
       </c>
       <c r="D97" t="n">
         <v>4.176591026354202e-05</v>
@@ -7707,7 +7707,7 @@
         <v>0.0002152915658761361</v>
       </c>
       <c r="K98" t="n">
-        <v>0.0002339929875877425</v>
+        <v>0.0002339929875877424</v>
       </c>
       <c r="L98" t="n">
         <v>0.0002691323329716332</v>
@@ -7722,7 +7722,7 @@
         <v>0.0002227646653815541</v>
       </c>
       <c r="P98" t="n">
-        <v>0.0006262770065537963</v>
+        <v>0.0006262770065537964</v>
       </c>
       <c r="Q98" t="n">
         <v>0.000387170147658347</v>
@@ -7777,13 +7777,13 @@
         <v>0.0001844248520312469</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0001557420327746176</v>
+        <v>0.0001557420327746177</v>
       </c>
       <c r="J99" t="n">
         <v>0.0001609972775719991</v>
       </c>
       <c r="K99" t="n">
-        <v>0.000155165714621872</v>
+        <v>0.0001551657146218721</v>
       </c>
       <c r="L99" t="n">
         <v>0.0002205912906044134</v>
@@ -7798,7 +7798,7 @@
         <v>0.0002702750725320505</v>
       </c>
       <c r="P99" t="n">
-        <v>0.0003162950248554443</v>
+        <v>0.0003162950248554444</v>
       </c>
       <c r="Q99" t="n">
         <v>0.0003126073709147826</v>
@@ -7807,7 +7807,7 @@
         <v>0.0003286154008536897</v>
       </c>
       <c r="S99" t="n">
-        <v>0.0003456296952921774</v>
+        <v>0.0003456296952921775</v>
       </c>
       <c r="T99" t="n">
         <v>0.0002773937289596063</v>
@@ -7822,7 +7822,7 @@
         <v>0.0004028307335074025</v>
       </c>
       <c r="X99" t="n">
-        <v>0.000421979638849727</v>
+        <v>0.0004219796388497271</v>
       </c>
     </row>
     <row r="100">
@@ -7856,7 +7856,7 @@
         <v>0.0005003350508621664</v>
       </c>
       <c r="J100" t="n">
-        <v>0.0005211796144554049</v>
+        <v>0.0005211796144554048</v>
       </c>
       <c r="K100" t="n">
         <v>0.0005026240602794663</v>
@@ -7874,7 +7874,7 @@
         <v>0.0004668868411967145</v>
       </c>
       <c r="P100" t="n">
-        <v>0.0004555600019562432</v>
+        <v>0.0004555600019562433</v>
       </c>
       <c r="Q100" t="n">
         <v>0.0004105520459557359</v>
@@ -7886,10 +7886,10 @@
         <v>0.0004634856453950335</v>
       </c>
       <c r="T100" t="n">
-        <v>0.0005429395802172527</v>
+        <v>0.0005429395802172526</v>
       </c>
       <c r="U100" t="n">
-        <v>0.0004891205705052004</v>
+        <v>0.0004891205705052003</v>
       </c>
       <c r="V100" t="n">
         <v>0.0004975895100505322</v>
@@ -7914,7 +7914,7 @@
         <v>0.0004754408786224647</v>
       </c>
       <c r="D101" t="n">
-        <v>0.000376557393871307</v>
+        <v>0.0003765573938713068</v>
       </c>
       <c r="E101" t="n">
         <v>0.0004976043936704928</v>
@@ -7923,7 +7923,7 @@
         <v>0.0003877542880625736</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0003556067310697972</v>
+        <v>0.0003556067310697971</v>
       </c>
       <c r="H101" t="n">
         <v>0.000423295748776168</v>
@@ -7950,22 +7950,22 @@
         <v>0.0004481353909997845</v>
       </c>
       <c r="P101" t="n">
-        <v>0.0003588165749030972</v>
+        <v>0.0003588165749030971</v>
       </c>
       <c r="Q101" t="n">
         <v>0.0003050883032985866</v>
       </c>
       <c r="R101" t="n">
-        <v>0.0002983074823829686</v>
+        <v>0.0002983074823829685</v>
       </c>
       <c r="S101" t="n">
         <v>0.000282943279097801</v>
       </c>
       <c r="T101" t="n">
-        <v>0.0002885794506006215</v>
+        <v>0.0002885794506006214</v>
       </c>
       <c r="U101" t="n">
-        <v>0.0002841023056194649</v>
+        <v>0.000284102305619465</v>
       </c>
       <c r="V101" t="n">
         <v>0.0003096666275934402</v>
@@ -7987,10 +7987,10 @@
         </is>
       </c>
       <c r="C102" t="n">
-        <v>0.005383648577304998</v>
+        <v>0.005383648577304996</v>
       </c>
       <c r="D102" t="n">
-        <v>0.005642707103456813</v>
+        <v>0.005642707103456812</v>
       </c>
       <c r="E102" t="n">
         <v>0.007001975263246205</v>
@@ -8002,7 +8002,7 @@
         <v>0.005490300895869524</v>
       </c>
       <c r="H102" t="n">
-        <v>0.006286064327938101</v>
+        <v>0.006286064327938102</v>
       </c>
       <c r="I102" t="n">
         <v>0.00593076748910547</v>
@@ -8011,7 +8011,7 @@
         <v>0.006158063293123467</v>
       </c>
       <c r="K102" t="n">
-        <v>0.006136057308095267</v>
+        <v>0.006136057308095266</v>
       </c>
       <c r="L102" t="n">
         <v>0.005560648228167624</v>
@@ -8035,7 +8035,7 @@
         <v>0.005700247838066504</v>
       </c>
       <c r="S102" t="n">
-        <v>0.005351437772198098</v>
+        <v>0.005351437772198097</v>
       </c>
       <c r="T102" t="n">
         <v>0.004929176843583375</v>
@@ -8063,7 +8063,7 @@
         </is>
       </c>
       <c r="C103" t="n">
-        <v>0.0002804739755443763</v>
+        <v>0.0002804739755443764</v>
       </c>
       <c r="D103" t="n">
         <v>4.365620571281373e-05</v>
@@ -8139,7 +8139,7 @@
         </is>
       </c>
       <c r="C104" t="n">
-        <v>0.000293717197323029</v>
+        <v>0.0002937171973230289</v>
       </c>
       <c r="D104" t="n">
         <v>0.0001831646577698979</v>
@@ -8175,7 +8175,7 @@
         <v>0.0002662315867659228</v>
       </c>
       <c r="O104" t="n">
-        <v>0.0002423881780465552</v>
+        <v>0.0002423881780465551</v>
       </c>
       <c r="P104" t="n">
         <v>0.0002698026886168974</v>
@@ -8224,10 +8224,10 @@
         <v>0.0009001347548821761</v>
       </c>
       <c r="F105" t="n">
-        <v>0.0008181891941938111</v>
+        <v>0.000818189194193811</v>
       </c>
       <c r="G105" t="n">
-        <v>0.0007591807925633112</v>
+        <v>0.0007591807925633111</v>
       </c>
       <c r="H105" t="n">
         <v>0.001007108214840085</v>
@@ -8245,7 +8245,7 @@
         <v>0.00093680172658507</v>
       </c>
       <c r="M105" t="n">
-        <v>0.00100160684938401</v>
+        <v>0.001001606849384011</v>
       </c>
       <c r="N105" t="n">
         <v>0.00100386479946656</v>
@@ -8257,10 +8257,10 @@
         <v>0.0007225577237046633</v>
       </c>
       <c r="Q105" t="n">
-        <v>0.0005636667485595567</v>
+        <v>0.0005636667485595565</v>
       </c>
       <c r="R105" t="n">
-        <v>0.0005082529924509945</v>
+        <v>0.0005082529924509944</v>
       </c>
       <c r="S105" t="n">
         <v>0.0005010789759291204</v>
@@ -8278,7 +8278,7 @@
         <v>0.0005058021209997525</v>
       </c>
       <c r="X105" t="n">
-        <v>0.0004753840095470099</v>
+        <v>0.00047538400954701</v>
       </c>
     </row>
     <row r="106">
@@ -8300,7 +8300,7 @@
         <v>0.0005159506205618147</v>
       </c>
       <c r="F106" t="n">
-        <v>0.000452392051919947</v>
+        <v>0.0004523920519199469</v>
       </c>
       <c r="G106" t="n">
         <v>0.0003998683771206568</v>
@@ -8318,7 +8318,7 @@
         <v>0.0005171087587348842</v>
       </c>
       <c r="L106" t="n">
-        <v>0.0006223257157798539</v>
+        <v>0.0006223257157798538</v>
       </c>
       <c r="M106" t="n">
         <v>0.0005898921295556141</v>
@@ -8327,10 +8327,10 @@
         <v>0.0004889316880467646</v>
       </c>
       <c r="O106" t="n">
-        <v>0.0004696609925327207</v>
+        <v>0.0004696609925327208</v>
       </c>
       <c r="P106" t="n">
-        <v>0.0004069294041652649</v>
+        <v>0.0004069294041652651</v>
       </c>
       <c r="Q106" t="n">
         <v>0.0004531710797137044</v>
@@ -8373,7 +8373,7 @@
         <v>0.0007279406200965884</v>
       </c>
       <c r="E107" t="n">
-        <v>0.0008773887668427698</v>
+        <v>0.0008773887668427697</v>
       </c>
       <c r="F107" t="n">
         <v>0.0007630439105383445</v>
@@ -8443,7 +8443,7 @@
         </is>
       </c>
       <c r="C108" t="n">
-        <v>0.002376160004569698</v>
+        <v>0.0023761600045697</v>
       </c>
       <c r="D108" t="n">
         <v>0.001780273222719914</v>
@@ -8464,13 +8464,13 @@
         <v>0.002276090755192429</v>
       </c>
       <c r="J108" t="n">
-        <v>0.002341432937797836</v>
+        <v>0.002341432937797837</v>
       </c>
       <c r="K108" t="n">
-        <v>0.002245014870387533</v>
+        <v>0.002245014870387534</v>
       </c>
       <c r="L108" t="n">
-        <v>0.002398977808634018</v>
+        <v>0.002398977808634017</v>
       </c>
       <c r="M108" t="n">
         <v>0.00228693276567507</v>
@@ -8482,16 +8482,16 @@
         <v>0.002119584735372715</v>
       </c>
       <c r="P108" t="n">
-        <v>0.00222404031586163</v>
+        <v>0.002224040315861631</v>
       </c>
       <c r="Q108" t="n">
         <v>0.001931688723616507</v>
       </c>
       <c r="R108" t="n">
-        <v>0.001825240901523925</v>
+        <v>0.001825240901523926</v>
       </c>
       <c r="S108" t="n">
-        <v>0.001652910715778377</v>
+        <v>0.001652910715778376</v>
       </c>
       <c r="T108" t="n">
         <v>0.001644521648169112</v>
@@ -8607,7 +8607,7 @@
         <v>0.0009021569236024718</v>
       </c>
       <c r="G110" t="n">
-        <v>0.0008843120008695087</v>
+        <v>0.0008843120008695085</v>
       </c>
       <c r="H110" t="n">
         <v>0.001127966102785243</v>
@@ -8625,7 +8625,7 @@
         <v>0.0008122539089982766</v>
       </c>
       <c r="M110" t="n">
-        <v>0.0008357439867525056</v>
+        <v>0.0008357439867525055</v>
       </c>
       <c r="N110" t="n">
         <v>0.0008810805894945903</v>
@@ -8634,31 +8634,31 @@
         <v>0.0009400220292646321</v>
       </c>
       <c r="P110" t="n">
-        <v>0.0007183087210862196</v>
+        <v>0.0007183087210862197</v>
       </c>
       <c r="Q110" t="n">
         <v>0.000761432305607727</v>
       </c>
       <c r="R110" t="n">
-        <v>0.000726992778205392</v>
+        <v>0.0007269927782053918</v>
       </c>
       <c r="S110" t="n">
         <v>0.0007330210384052892</v>
       </c>
       <c r="T110" t="n">
-        <v>0.0007702906306558484</v>
+        <v>0.0007702906306558482</v>
       </c>
       <c r="U110" t="n">
         <v>0.0006828289298448814</v>
       </c>
       <c r="V110" t="n">
-        <v>0.0007962635237058016</v>
+        <v>0.0007962635237058017</v>
       </c>
       <c r="W110" t="n">
         <v>0.0006727895985203919</v>
       </c>
       <c r="X110" t="n">
-        <v>0.0007939460637640331</v>
+        <v>0.0007939460637640332</v>
       </c>
     </row>
     <row r="111">
@@ -8677,34 +8677,34 @@
         <v>0.004640031743224621</v>
       </c>
       <c r="E111" t="n">
-        <v>0.0057471502366792</v>
+        <v>0.005747150236679198</v>
       </c>
       <c r="F111" t="n">
         <v>0.004908646732375429</v>
       </c>
       <c r="G111" t="n">
-        <v>0.004982394246174695</v>
+        <v>0.004982394246174696</v>
       </c>
       <c r="H111" t="n">
-        <v>0.005927924840914216</v>
+        <v>0.005927924840914217</v>
       </c>
       <c r="I111" t="n">
-        <v>0.00554858036182594</v>
+        <v>0.005548580361825938</v>
       </c>
       <c r="J111" t="n">
-        <v>0.005325656267364326</v>
+        <v>0.005325656267364327</v>
       </c>
       <c r="K111" t="n">
-        <v>0.005647354667191749</v>
+        <v>0.005647354667191751</v>
       </c>
       <c r="L111" t="n">
         <v>0.005999739778370839</v>
       </c>
       <c r="M111" t="n">
-        <v>0.005741279830045131</v>
+        <v>0.005741279830045132</v>
       </c>
       <c r="N111" t="n">
-        <v>0.005768264012975307</v>
+        <v>0.005768264012975308</v>
       </c>
       <c r="O111" t="n">
         <v>0.005574684899045811</v>
@@ -8713,13 +8713,13 @@
         <v>0.006849254782290661</v>
       </c>
       <c r="Q111" t="n">
-        <v>0.007612222128277111</v>
+        <v>0.007612222128277113</v>
       </c>
       <c r="R111" t="n">
-        <v>0.00743451524042429</v>
+        <v>0.007434515240424289</v>
       </c>
       <c r="S111" t="n">
-        <v>0.007200095077614502</v>
+        <v>0.0072000950776145</v>
       </c>
       <c r="T111" t="n">
         <v>0.006346551125906162</v>
@@ -8734,7 +8734,7 @@
         <v>0.006865763116269347</v>
       </c>
       <c r="X111" t="n">
-        <v>0.007094459588780194</v>
+        <v>0.007094459588780193</v>
       </c>
     </row>
     <row r="112">
@@ -8747,7 +8747,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0.001789715360811436</v>
+        <v>0.001789715360811435</v>
       </c>
       <c r="D112" t="n">
         <v>0.001653699206253505</v>
@@ -8914,7 +8914,7 @@
         <v>0.000243809020809907</v>
       </c>
       <c r="H114" t="n">
-        <v>0.000340076152427262</v>
+        <v>0.0003400761524272619</v>
       </c>
       <c r="I114" t="n">
         <v>0.0002877860866537265</v>
@@ -8996,13 +8996,13 @@
         <v>0.003065413876681442</v>
       </c>
       <c r="J115" t="n">
-        <v>0.003382546662190731</v>
+        <v>0.003382546662190732</v>
       </c>
       <c r="K115" t="n">
         <v>0.003172495367718363</v>
       </c>
       <c r="L115" t="n">
-        <v>0.003551046388183745</v>
+        <v>0.003551046388183746</v>
       </c>
       <c r="M115" t="n">
         <v>0.003690705909254795</v>
@@ -9011,7 +9011,7 @@
         <v>0.003906502643215127</v>
       </c>
       <c r="O115" t="n">
-        <v>0.003545832527322502</v>
+        <v>0.003545832527322503</v>
       </c>
       <c r="P115" t="n">
         <v>0.002201122526730635</v>
@@ -9038,7 +9038,7 @@
         <v>0.002261019196148322</v>
       </c>
       <c r="X115" t="n">
-        <v>0.002659726117605737</v>
+        <v>0.002659726117605736</v>
       </c>
     </row>
     <row r="116">
@@ -9142,7 +9142,7 @@
         <v>0.0006192458748136881</v>
       </c>
       <c r="H117" t="n">
-        <v>0.0006808924939901364</v>
+        <v>0.0006808924939901363</v>
       </c>
       <c r="I117" t="n">
         <v>0.0006488573409808243</v>
@@ -9151,7 +9151,7 @@
         <v>0.0007424832194507039</v>
       </c>
       <c r="K117" t="n">
-        <v>0.000629916576305243</v>
+        <v>0.0006299165763052429</v>
       </c>
       <c r="L117" t="n">
         <v>0.0006752212304585077</v>
@@ -9242,7 +9242,7 @@
         <v>0.002179331185421132</v>
       </c>
       <c r="D119" t="n">
-        <v>0.001221382691918052</v>
+        <v>0.001221382691918053</v>
       </c>
       <c r="E119" t="n">
         <v>0.001190026940380092</v>
@@ -9281,7 +9281,7 @@
         <v>0.002604327270052277</v>
       </c>
       <c r="Q119" t="n">
-        <v>0.002589468949202408</v>
+        <v>0.002589468949202407</v>
       </c>
       <c r="R119" t="n">
         <v>0.002785054180863254</v>
@@ -9299,7 +9299,7 @@
         <v>0.0013153666949643</v>
       </c>
       <c r="W119" t="n">
-        <v>0.00315961935690824</v>
+        <v>0.003159619356908239</v>
       </c>
       <c r="X119" t="n">
         <v>0.002474206840696679</v>
@@ -9315,25 +9315,25 @@
         </is>
       </c>
       <c r="C120" t="n">
-        <v>0.06879439608444481</v>
+        <v>0.06879439608444485</v>
       </c>
       <c r="D120" t="n">
-        <v>0.03722528215917641</v>
+        <v>0.0372252821591764</v>
       </c>
       <c r="E120" t="n">
-        <v>0.05045834329247648</v>
+        <v>0.05045834329247647</v>
       </c>
       <c r="F120" t="n">
-        <v>0.06071064955812084</v>
+        <v>0.06071064955812085</v>
       </c>
       <c r="G120" t="n">
-        <v>0.0691016605177316</v>
+        <v>0.06910166051773159</v>
       </c>
       <c r="H120" t="n">
         <v>0.041271853832389</v>
       </c>
       <c r="I120" t="n">
-        <v>0.05952483004893746</v>
+        <v>0.05952483004893745</v>
       </c>
       <c r="J120" t="n">
         <v>0.06199244348220399</v>
@@ -9342,43 +9342,43 @@
         <v>0.06635624299269319</v>
       </c>
       <c r="L120" t="n">
-        <v>0.05467827706513462</v>
+        <v>0.05467827706513463</v>
       </c>
       <c r="M120" t="n">
-        <v>0.06162207376568919</v>
+        <v>0.0616220737656892</v>
       </c>
       <c r="N120" t="n">
-        <v>0.07474748170508007</v>
+        <v>0.07474748170508008</v>
       </c>
       <c r="O120" t="n">
-        <v>0.07575866874523529</v>
+        <v>0.07575866874523528</v>
       </c>
       <c r="P120" t="n">
-        <v>0.08815525826436416</v>
+        <v>0.08815525826436414</v>
       </c>
       <c r="Q120" t="n">
-        <v>0.08608419634335705</v>
+        <v>0.08608419634335704</v>
       </c>
       <c r="R120" t="n">
         <v>0.08417514847417817</v>
       </c>
       <c r="S120" t="n">
-        <v>0.06928894403397284</v>
+        <v>0.06928894403397286</v>
       </c>
       <c r="T120" t="n">
-        <v>0.07612182662709827</v>
+        <v>0.07612182662709828</v>
       </c>
       <c r="U120" t="n">
-        <v>0.07936546595926461</v>
+        <v>0.07936546595926459</v>
       </c>
       <c r="V120" t="n">
-        <v>0.07734557915715631</v>
+        <v>0.07734557915715633</v>
       </c>
       <c r="W120" t="n">
-        <v>0.07865320071249417</v>
+        <v>0.07865320071249414</v>
       </c>
       <c r="X120" t="n">
-        <v>0.07294990711736084</v>
+        <v>0.07294990711736082</v>
       </c>
     </row>
     <row r="121">
@@ -9391,7 +9391,7 @@
         </is>
       </c>
       <c r="C121" t="n">
-        <v>6.162513792907516e-05</v>
+        <v>6.162513792907518e-05</v>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr"/>
@@ -9427,7 +9427,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>0.0005920141697549184</v>
+        <v>0.0005920141697549185</v>
       </c>
       <c r="D122" t="n">
         <v>0.0004220641234256433</v>
@@ -9466,7 +9466,7 @@
         <v>0.0004478716152594924</v>
       </c>
       <c r="P122" t="n">
-        <v>0.0001362653113138194</v>
+        <v>0.0001362653113138193</v>
       </c>
       <c r="Q122" t="n">
         <v>4.194339977471851e-05</v>
@@ -9515,7 +9515,7 @@
         <v>0.003005167561454376</v>
       </c>
       <c r="G123" t="n">
-        <v>0.002828961965072037</v>
+        <v>0.002828961965072036</v>
       </c>
       <c r="H123" t="n">
         <v>0.002670246242819891</v>
@@ -9524,7 +9524,7 @@
         <v>0.002803675042420911</v>
       </c>
       <c r="J123" t="n">
-        <v>0.002872179102477239</v>
+        <v>0.00287217910247724</v>
       </c>
       <c r="K123" t="n">
         <v>0.003058624147421942</v>
@@ -9536,7 +9536,7 @@
         <v>0.003091791297458921</v>
       </c>
       <c r="N123" t="n">
-        <v>0.00321765445256018</v>
+        <v>0.003217654452560181</v>
       </c>
       <c r="O123" t="n">
         <v>0.003109151056680921</v>
@@ -9551,7 +9551,7 @@
         <v>0.003221769007620358</v>
       </c>
       <c r="S123" t="n">
-        <v>0.003255444287921536</v>
+        <v>0.003255444287921535</v>
       </c>
       <c r="T123" t="n">
         <v>0.00325044147692993</v>
@@ -9563,7 +9563,7 @@
         <v>0.003379153443685646</v>
       </c>
       <c r="W123" t="n">
-        <v>0.003172086048521637</v>
+        <v>0.003172086048521638</v>
       </c>
       <c r="X123" t="n">
         <v>0.003319621386371275</v>
@@ -9612,7 +9612,7 @@
         <v>0.001639586959714758</v>
       </c>
       <c r="N124" t="n">
-        <v>0.0017817031058366</v>
+        <v>0.001781703105836599</v>
       </c>
       <c r="O124" t="n">
         <v>0.00161328028855557</v>
@@ -9655,7 +9655,7 @@
         </is>
       </c>
       <c r="C125" t="n">
-        <v>0.0004927345621930003</v>
+        <v>0.0004927345621930001</v>
       </c>
       <c r="D125" t="n">
         <v>0.0003913476397494523</v>
@@ -9743,7 +9743,7 @@
         <v>0.0008060475534775707</v>
       </c>
       <c r="G126" t="n">
-        <v>0.0007538862313114762</v>
+        <v>0.0007538862313114763</v>
       </c>
       <c r="H126" t="n">
         <v>0.0007619083707958462</v>
@@ -9752,10 +9752,10 @@
         <v>0.0006863307432280481</v>
       </c>
       <c r="J126" t="n">
-        <v>0.0007369858139134211</v>
+        <v>0.000736985813913421</v>
       </c>
       <c r="K126" t="n">
-        <v>0.0007994039972936963</v>
+        <v>0.0007994039972936964</v>
       </c>
       <c r="L126" t="n">
         <v>0.0008373706393670397</v>
@@ -9764,7 +9764,7 @@
         <v>0.0008351457958153747</v>
       </c>
       <c r="N126" t="n">
-        <v>0.0008631657754410694</v>
+        <v>0.0008631657754410695</v>
       </c>
       <c r="O126" t="n">
         <v>0.0007897998970611911</v>
@@ -9807,7 +9807,7 @@
         </is>
       </c>
       <c r="C127" t="n">
-        <v>0.0006047454803347096</v>
+        <v>0.0006047454803347095</v>
       </c>
       <c r="D127" t="n">
         <v>0.0002604820756193494</v>
@@ -9846,7 +9846,7 @@
         <v>0.0003478121566458219</v>
       </c>
       <c r="P127" t="n">
-        <v>0.0006214257370455167</v>
+        <v>0.0006214257370455168</v>
       </c>
       <c r="Q127" t="n">
         <v>0.0004931178036675693</v>
@@ -9855,7 +9855,7 @@
         <v>0.0004854226132883493</v>
       </c>
       <c r="S127" t="n">
-        <v>0.0004897750073561881</v>
+        <v>0.0004897750073561879</v>
       </c>
       <c r="T127" t="n">
         <v>0.0005452796257517699</v>
@@ -10001,28 +10001,28 @@
         <v>0.000741025002280943</v>
       </c>
       <c r="Q129" t="n">
-        <v>0.0007956665488832048</v>
+        <v>0.0007956665488832046</v>
       </c>
       <c r="R129" t="n">
-        <v>0.0007056518248122638</v>
+        <v>0.0007056518248122639</v>
       </c>
       <c r="S129" t="n">
-        <v>0.0006955576265182257</v>
+        <v>0.0006955576265182256</v>
       </c>
       <c r="T129" t="n">
         <v>0.0007160799065559844</v>
       </c>
       <c r="U129" t="n">
-        <v>0.0007213612715475288</v>
+        <v>0.0007213612715475286</v>
       </c>
       <c r="V129" t="n">
         <v>0.0007252761628889811</v>
       </c>
       <c r="W129" t="n">
-        <v>0.0006990929125636884</v>
+        <v>0.0006990929125636885</v>
       </c>
       <c r="X129" t="n">
-        <v>0.0007730365799001263</v>
+        <v>0.0007730365799001262</v>
       </c>
     </row>
     <row r="130">
@@ -10035,10 +10035,10 @@
         </is>
       </c>
       <c r="C130" t="n">
-        <v>0.0007243762892396155</v>
+        <v>0.0007243762892396156</v>
       </c>
       <c r="D130" t="n">
-        <v>0.0006076236863841703</v>
+        <v>0.0006076236863841704</v>
       </c>
       <c r="E130" t="n">
         <v>0.0006454596269849672</v>
@@ -10047,7 +10047,7 @@
         <v>0.0007570925223609458</v>
       </c>
       <c r="G130" t="n">
-        <v>0.0006817185674057028</v>
+        <v>0.0006817185674057029</v>
       </c>
       <c r="H130" t="n">
         <v>0.0008125746757787012</v>
@@ -10056,7 +10056,7 @@
         <v>0.0006988102089161621</v>
       </c>
       <c r="J130" t="n">
-        <v>0.0007579918323757596</v>
+        <v>0.0007579918323757595</v>
       </c>
       <c r="K130" t="n">
         <v>0.0007297910136736285</v>
@@ -10065,13 +10065,13 @@
         <v>0.0008686354728200393</v>
       </c>
       <c r="M130" t="n">
-        <v>0.000813904524706904</v>
+        <v>0.0008139045247069041</v>
       </c>
       <c r="N130" t="n">
         <v>0.000836039292559027</v>
       </c>
       <c r="O130" t="n">
-        <v>0.0007745713341156862</v>
+        <v>0.0007745713341156864</v>
       </c>
       <c r="P130" t="n">
         <v>0.000730900639498979</v>
@@ -10089,16 +10089,16 @@
         <v>0.0006089214477233124</v>
       </c>
       <c r="U130" t="n">
-        <v>0.0006177486459868536</v>
+        <v>0.0006177486459868537</v>
       </c>
       <c r="V130" t="n">
-        <v>0.0007208462871918416</v>
+        <v>0.0007208462871918415</v>
       </c>
       <c r="W130" t="n">
         <v>0.0006354312382307192</v>
       </c>
       <c r="X130" t="n">
-        <v>0.0006645388700485898</v>
+        <v>0.0006645388700485899</v>
       </c>
     </row>
     <row r="131">
@@ -10120,16 +10120,16 @@
         <v>0.0005554597925878673</v>
       </c>
       <c r="F131" t="n">
-        <v>0.000449408159018573</v>
+        <v>0.0004494081590185729</v>
       </c>
       <c r="G131" t="n">
         <v>0.0004201136587448083</v>
       </c>
       <c r="H131" t="n">
-        <v>0.0004483360889736434</v>
+        <v>0.0004483360889736433</v>
       </c>
       <c r="I131" t="n">
-        <v>0.000472265700395237</v>
+        <v>0.0004722657003952371</v>
       </c>
       <c r="J131" t="n">
         <v>0.0004582533406382882</v>
@@ -10162,7 +10162,7 @@
         <v>0.0003554704574081722</v>
       </c>
       <c r="T131" t="n">
-        <v>0.000425885750349561</v>
+        <v>0.0004258857503495611</v>
       </c>
       <c r="U131" t="n">
         <v>0.0004278374354758775</v>
@@ -10263,22 +10263,22 @@
         </is>
       </c>
       <c r="C133" t="n">
-        <v>0.008568304621855566</v>
+        <v>0.008568304621855568</v>
       </c>
       <c r="D133" t="n">
         <v>0.007661117843809303</v>
       </c>
       <c r="E133" t="n">
-        <v>0.008732171184646075</v>
+        <v>0.008732171184646073</v>
       </c>
       <c r="F133" t="n">
         <v>0.01018014971129171</v>
       </c>
       <c r="G133" t="n">
-        <v>0.009662655158774394</v>
+        <v>0.009662655158774392</v>
       </c>
       <c r="H133" t="n">
-        <v>0.006002109929332244</v>
+        <v>0.006002109929332245</v>
       </c>
       <c r="I133" t="n">
         <v>0.00891265622638363</v>
@@ -10290,7 +10290,7 @@
         <v>0.009630606465660687</v>
       </c>
       <c r="L133" t="n">
-        <v>0.007061256196965752</v>
+        <v>0.007061256196965751</v>
       </c>
       <c r="M133" t="n">
         <v>0.009334545649048107</v>
@@ -10339,7 +10339,7 @@
         </is>
       </c>
       <c r="C134" t="n">
-        <v>6.416281523180725e-05</v>
+        <v>6.416281523180726e-05</v>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr"/>
@@ -10466,7 +10466,7 @@
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="n">
-        <v>7.767625251821777e-05</v>
+        <v>7.767625251821778e-05</v>
       </c>
       <c r="Q136" t="inlineStr"/>
       <c r="R136" t="inlineStr"/>
@@ -10602,7 +10602,7 @@
         <v>4.486621685844016e-05</v>
       </c>
       <c r="P138" t="n">
-        <v>0.0001514558843192907</v>
+        <v>0.0001514558843192908</v>
       </c>
       <c r="Q138" t="inlineStr"/>
       <c r="R138" t="inlineStr"/>
